--- a/config/data/ContentIdentity.xlsx
+++ b/config/data/ContentIdentity.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N761"/>
+  <dimension ref="A1:N766"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31437,12 +31437,12 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Meteoric Sunder Hit Plan</t>
+          <t>Meteoric Sunder Hit Plan 1</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>披星百裂命中计划</t>
+          <t>披星百裂命中计划1</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
@@ -31500,12 +31500,12 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Rosy-Fingered Hit Plan</t>
+          <t>Rosy-Fingered Hit Plan 1</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>金玫之指命中计划</t>
+          <t>金玫之指命中计划1</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
@@ -31563,12 +31563,12 @@
       </c>
       <c r="E479" t="inlineStr">
         <is>
-          <t>Slash by a Thousandfold Kiss Hit Plan</t>
+          <t>Slash by a Thousandfold Kiss Hit Plan 1</t>
         </is>
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>孤锋千吻命中计划</t>
+          <t>孤锋千吻命中计划1</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
@@ -31626,12 +31626,12 @@
       </c>
       <c r="E480" t="inlineStr">
         <is>
-          <t>Thorned Nectar Hit Plan</t>
+          <t>Thorned Nectar Hit Plan 1</t>
         </is>
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>刺纹之蜜命中计划</t>
+          <t>刺纹之蜜命中计划1</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
@@ -31689,12 +31689,12 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Meteor Storm Hit Plan</t>
+          <t>Meteor Storm Hit Plan 1</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>流星群落命中计划</t>
+          <t>流星群落命中计划1</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
@@ -31752,12 +31752,12 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Miracle Flash Hit Plan</t>
+          <t>Miracle Flash Hit Plan 1</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>灵光一现命中计划</t>
+          <t>灵光一现命中计划1</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
@@ -31815,12 +31815,12 @@
       </c>
       <c r="E483" t="inlineStr">
         <is>
-          <t>Spectrum Beam Hit Plan</t>
+          <t>Spectrum Beam Hit Plan 1</t>
         </is>
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>光谱射线命中计划</t>
+          <t>光谱射线命中计划1</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
@@ -31878,12 +31878,12 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Because We're Family Hit Plan</t>
+          <t>Because We're Family Hit Plan 1</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>因为我们是家人命中计划</t>
+          <t>因为我们是家人命中计划1</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -31941,12 +31941,12 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>I Want to Help Hit Plan</t>
+          <t>I Want to Help Hit Plan 1</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>我也想帮上忙命中计划</t>
+          <t>我也想帮上忙命中计划1</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -32004,12 +32004,12 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Promise, Not Command Hit Plan</t>
+          <t>Promise, Not Command Hit Plan 1</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>是约定不是命令命中计划</t>
+          <t>是约定不是命令命中计划1</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -32067,12 +32067,12 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Svarog Watches Over You Hit Plan</t>
+          <t>Svarog Watches Over You Hit Plan 1</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>史瓦罗在看着你命中计划</t>
+          <t>史瓦罗在看着你命中计划1</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -32130,12 +32130,12 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Chrysalid Pyronexus Hit Plan</t>
+          <t>Chrysalid Pyronexus Hit Plan 1</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>茧式源火中枢命中计划</t>
+          <t>茧式源火中枢命中计划1</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -32193,12 +32193,12 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Fyrefly Type-IV: Complete Combustion Hit Plan</t>
+          <t>Fyrefly Type-IV: Complete Combustion Hit Plan 1</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>火萤Ⅳ型-完全燃烧命中计划</t>
+          <t>火萤Ⅳ型-完全燃烧命中计划1</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -32256,12 +32256,12 @@
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Fyrefly Type-IV: Deathstar Overload Hit Plan</t>
+          <t>Fyrefly Type-IV: Deathstar Overload Hit Plan 1</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>火萤Ⅳ型-死星过载命中计划</t>
+          <t>火萤Ⅳ型-死星过载命中计划1</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -32319,12 +32319,12 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Fyrefly Type-IV: Pyrogenic Decimation Hit Plan</t>
+          <t>Fyrefly Type-IV: Pyrogenic Decimation Hit Plan 1</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>火萤Ⅳ型-底火斩击命中计划</t>
+          <t>火萤Ⅳ型-底火斩击命中计划1</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
@@ -32382,12 +32382,12 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Order: Aerial Bombardment Hit Plan</t>
+          <t>Order: Aerial Bombardment Hit Plan 1</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>指令-天火轰击命中计划</t>
+          <t>指令-天火轰击命中计划1</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
@@ -32445,12 +32445,12 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Order: Flare Propulsion Hit Plan</t>
+          <t>Order: Flare Propulsion Hit Plan 1</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>指令-闪燃推进命中计划</t>
+          <t>指令-闪燃推进命中计划1</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
@@ -32508,12 +32508,12 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Δ Order: Meteoric Incineration Hit Plan</t>
+          <t>Δ Order: Meteoric Incineration Hit Plan 1</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>Δ指令-焦土陨击命中计划</t>
+          <t>Δ指令-焦土陨击命中计划1</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
@@ -32571,12 +32571,12 @@
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Caressing Moonlight Hit Plan</t>
+          <t>Caressing Moonlight Hit Plan 1</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>月光摩挲连绵命中计划</t>
+          <t>月光摩挲连绵命中计划1</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
@@ -32634,12 +32634,12 @@
       </c>
       <c r="E496" t="inlineStr">
         <is>
-          <t>Gentle but Cruel Hit Plan</t>
+          <t>Gentle but Cruel Hit Plan 1</t>
         </is>
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>温柔亦同残酷命中计划</t>
+          <t>温柔亦同残酷命中计划1</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
@@ -32697,12 +32697,12 @@
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Mercy Is Not Forgiveness Hit Plan</t>
+          <t>Mercy Is Not Forgiveness Hit Plan 1</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>宽恕无关慈悲命中计划</t>
+          <t>宽恕无关慈悲命中计划1</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
@@ -32760,12 +32760,12 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Midnight Tumult Hit Plan</t>
+          <t>Midnight Tumult Hit Plan 1</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>夜间喧嚣不止命中计划</t>
+          <t>夜间喧嚣不止命中计划1</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
@@ -32823,12 +32823,12 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Twilight Trill Hit Plan</t>
+          <t>Twilight Trill Hit Plan 1</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>悲剧尽头的颤音命中计划</t>
+          <t>悲剧尽头的颤音命中计划1</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
@@ -32886,12 +32886,12 @@
       </c>
       <c r="E500" t="inlineStr">
         <is>
-          <t>Bonus Stage: αWolf Instant Hit Plan</t>
+          <t>Bonus Stage: αWolf Instant Hit Plan 1</t>
         </is>
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>奖励关：「狼尊时刻」命中计划</t>
+          <t>奖励关：「狼尊时刻」命中计划1</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
@@ -32949,12 +32949,12 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>God Mode: ON! Hit Plan</t>
+          <t>God Mode: ON! Hit Plan 1</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>无敌玩家，启动！命中计划</t>
+          <t>无敌玩家，启动！命中计划1</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
@@ -33012,12 +33012,12 @@
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Honkai-DMG Demo Hit Plan</t>
+          <t>Honkai-DMG Demo Hit Plan 1</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>崩坏级伤害演示命中计划</t>
+          <t>崩坏级伤害演示命中计划1</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
@@ -33075,12 +33075,12 @@
       </c>
       <c r="E503" t="inlineStr">
         <is>
-          <t>I Carry, We Win Hit Plan</t>
+          <t>I Carry, We Win Hit Plan 1</t>
         </is>
       </c>
       <c r="F503" t="inlineStr">
         <is>
-          <t>有我在，把把都是顺风局命中计划</t>
+          <t>有我在，把把都是顺风局命中计划1</t>
         </is>
       </c>
       <c r="G503" t="inlineStr">
@@ -33138,12 +33138,12 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>One Punch! Hit Plan</t>
+          <t>One Punch! Hit Plan 1</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>拳头硬了！命中计划</t>
+          <t>拳头硬了！命中计划1</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
@@ -33201,12 +33201,12 @@
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>This? Absolute Meta! Hit Plan</t>
+          <t>This? Absolute Meta! Hit Plan 1</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>朋友，这才是T0级秘技命中计划</t>
+          <t>朋友，这才是T0级秘技命中计划1</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -33264,12 +33264,12 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Trigger Happy Hit Plan</t>
+          <t>Trigger Happy Hit Plan 1</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>Shoot属性大爆发命中计划</t>
+          <t>Shoot属性大爆发命中计划1</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
@@ -33313,31 +33313,31 @@
     </row>
     <row r="507">
       <c r="B507" t="n">
-        <v>22001</v>
+        <v>21990</v>
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.01.trace-1</t>
+          <t>program.hit-plan.character.silver-wolf-lv-999.ability.bonus-stage-αwolf-instant.normal.phase-2</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Trace</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>Bonus Stage: αWolf Instant Hit Plan 2</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>奖励关：「狼尊时刻」命中计划2</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>Complete battle-relevant Trace identity, graph edge and prepared mechanic payload.</t>
+          <t>Ordered hit and Toughness-share structure transcribed from the prepared ability record.</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -33376,31 +33376,31 @@
     </row>
     <row r="508">
       <c r="B508" t="n">
-        <v>22002</v>
+        <v>21991</v>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.02.trace-2</t>
+          <t>program.hit-plan.character.silver-wolf-lv-999.ability.bonus-stage-αwolf-instant.normal.phase-3</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Trace</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>Bonus Stage: αWolf Instant Hit Plan 3</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>奖励关：「狼尊时刻」命中计划3</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>Complete battle-relevant Trace identity, graph edge and prepared mechanic payload.</t>
+          <t>Ordered hit and Toughness-share structure transcribed from the prepared ability record.</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -33439,31 +33439,31 @@
     </row>
     <row r="509">
       <c r="B509" t="n">
-        <v>22003</v>
+        <v>21992</v>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.03.trace-3</t>
+          <t>program.hit-plan.character.silver-wolf-lv-999.ability.bonus-stage-αwolf-instant.normal.phase-4</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Trace</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>Bonus Stage: αWolf Instant Hit Plan 4</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>奖励关：「狼尊时刻」命中计划4</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>Complete battle-relevant Trace identity, graph edge and prepared mechanic payload.</t>
+          <t>Ordered hit and Toughness-share structure transcribed from the prepared ability record.</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -33502,11 +33502,11 @@
     </row>
     <row r="510">
       <c r="B510" t="n">
-        <v>22004</v>
+        <v>22001</v>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.04.trace-4</t>
+          <t>character.aglaea.trace.01.trace-1</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -33516,12 +33516,12 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
@@ -33565,11 +33565,11 @@
     </row>
     <row r="511">
       <c r="B511" t="n">
-        <v>22005</v>
+        <v>22002</v>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.05.trace-5</t>
+          <t>character.aglaea.trace.02.trace-2</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -33579,12 +33579,12 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
@@ -33628,11 +33628,11 @@
     </row>
     <row r="512">
       <c r="B512" t="n">
-        <v>22006</v>
+        <v>22003</v>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.06.the-myopics-doom</t>
+          <t>character.aglaea.trace.03.trace-3</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -33642,12 +33642,12 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>The Myopic's Doom</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>短视之惩</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
@@ -33691,11 +33691,11 @@
     </row>
     <row r="513">
       <c r="B513" t="n">
-        <v>22007</v>
+        <v>22004</v>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.07.last-thread-of-fate</t>
+          <t>character.aglaea.trace.04.trace-4</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -33705,12 +33705,12 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Last Thread of Fate</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>织运之竭</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -33754,11 +33754,11 @@
     </row>
     <row r="514">
       <c r="B514" t="n">
-        <v>22008</v>
+        <v>22005</v>
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.08.the-speeding-sol</t>
+          <t>character.aglaea.trace.05.trace-5</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -33768,12 +33768,12 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>The Speeding Sol</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>飞驰之阳</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
@@ -33817,11 +33817,11 @@
     </row>
     <row r="515">
       <c r="B515" t="n">
-        <v>22009</v>
+        <v>22006</v>
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.09.dmg-boost-lightning</t>
+          <t>character.aglaea.trace.06.the-myopics-doom</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -33831,12 +33831,12 @@
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>DMG Boost: Lightning</t>
+          <t>The Myopic's Doom</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>伤害强化•雷</t>
+          <t>短视之惩</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -33880,11 +33880,11 @@
     </row>
     <row r="516">
       <c r="B516" t="n">
-        <v>22010</v>
+        <v>22007</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.10.crit-rate-boost</t>
+          <t>character.aglaea.trace.07.last-thread-of-fate</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -33894,12 +33894,12 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost</t>
+          <t>Last Thread of Fate</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>暴击率强化</t>
+          <t>织运之竭</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
@@ -33943,11 +33943,11 @@
     </row>
     <row r="517">
       <c r="B517" t="n">
-        <v>22011</v>
+        <v>22008</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.11.dmg-boost-lightning</t>
+          <t>character.aglaea.trace.08.the-speeding-sol</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -33957,12 +33957,12 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>DMG Boost: Lightning</t>
+          <t>The Speeding Sol</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>伤害强化•雷</t>
+          <t>飞驰之阳</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -34006,11 +34006,11 @@
     </row>
     <row r="518">
       <c r="B518" t="n">
-        <v>22012</v>
+        <v>22009</v>
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.12.def-boost</t>
+          <t>character.aglaea.trace.09.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -34020,12 +34020,12 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>DEF Boost</t>
+          <t>DMG Boost: Lightning</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>防御强化</t>
+          <t>伤害强化•雷</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -34069,11 +34069,11 @@
     </row>
     <row r="519">
       <c r="B519" t="n">
-        <v>22013</v>
+        <v>22010</v>
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.13.dmg-boost-lightning</t>
+          <t>character.aglaea.trace.10.crit-rate-boost</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -34083,12 +34083,12 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>DMG Boost: Lightning</t>
+          <t>CRIT Rate Boost</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>伤害强化•雷</t>
+          <t>暴击率强化</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -34132,11 +34132,11 @@
     </row>
     <row r="520">
       <c r="B520" t="n">
-        <v>22014</v>
+        <v>22011</v>
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.14.crit-rate-boost</t>
+          <t>character.aglaea.trace.11.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -34146,12 +34146,12 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost</t>
+          <t>DMG Boost: Lightning</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>暴击率强化</t>
+          <t>伤害强化•雷</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -34195,11 +34195,11 @@
     </row>
     <row r="521">
       <c r="B521" t="n">
-        <v>22015</v>
+        <v>22012</v>
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.15.dmg-boost-lightning</t>
+          <t>character.aglaea.trace.12.def-boost</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -34209,12 +34209,12 @@
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>DMG Boost: Lightning</t>
+          <t>DEF Boost</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>伤害强化•雷</t>
+          <t>防御强化</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -34258,11 +34258,11 @@
     </row>
     <row r="522">
       <c r="B522" t="n">
-        <v>22016</v>
+        <v>22013</v>
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.16.def-boost</t>
+          <t>character.aglaea.trace.13.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -34272,12 +34272,12 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>DEF Boost</t>
+          <t>DMG Boost: Lightning</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>防御强化</t>
+          <t>伤害强化•雷</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -34321,11 +34321,11 @@
     </row>
     <row r="523">
       <c r="B523" t="n">
-        <v>22017</v>
+        <v>22014</v>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.17.crit-rate-boost</t>
+          <t>character.aglaea.trace.14.crit-rate-boost</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
@@ -34384,11 +34384,11 @@
     </row>
     <row r="524">
       <c r="B524" t="n">
-        <v>22018</v>
+        <v>22015</v>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.18.dmg-boost-lightning</t>
+          <t>character.aglaea.trace.15.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
@@ -34447,11 +34447,11 @@
     </row>
     <row r="525">
       <c r="B525" t="n">
-        <v>22019</v>
+        <v>22016</v>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.19.thorned-snare</t>
+          <t>character.aglaea.trace.16.def-boost</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -34461,12 +34461,12 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Thorned Snare</t>
+          <t>DEF Boost</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>刺纹之陷</t>
+          <t>防御强化</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
@@ -34510,11 +34510,11 @@
     </row>
     <row r="526">
       <c r="B526" t="n">
-        <v>22020</v>
+        <v>22017</v>
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>character.aglaea.trace.20.a-body-brewed-by-tears</t>
+          <t>character.aglaea.trace.17.crit-rate-boost</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -34524,12 +34524,12 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>A Body Brewed by Tears</t>
+          <t>CRIT Rate Boost</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>泪水锻造的匠躯</t>
+          <t>暴击率强化</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -34573,11 +34573,11 @@
     </row>
     <row r="527">
       <c r="B527" t="n">
-        <v>22021</v>
+        <v>22018</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>character.asta.trace.01.trace-1</t>
+          <t>character.aglaea.trace.18.dmg-boost-lightning</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -34587,12 +34587,12 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>DMG Boost: Lightning</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>伤害强化•雷</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -34636,11 +34636,11 @@
     </row>
     <row r="528">
       <c r="B528" t="n">
-        <v>22022</v>
+        <v>22019</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>character.asta.trace.02.trace-2</t>
+          <t>character.aglaea.trace.19.thorned-snare</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -34650,12 +34650,12 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>Thorned Snare</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>刺纹之陷</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -34699,11 +34699,11 @@
     </row>
     <row r="529">
       <c r="B529" t="n">
-        <v>22023</v>
+        <v>22020</v>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>character.asta.trace.03.trace-3</t>
+          <t>character.aglaea.trace.20.a-body-brewed-by-tears</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -34713,12 +34713,12 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>A Body Brewed by Tears</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>泪水锻造的匠躯</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
@@ -34762,11 +34762,11 @@
     </row>
     <row r="530">
       <c r="B530" t="n">
-        <v>22024</v>
+        <v>22021</v>
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>character.asta.trace.04.trace-4</t>
+          <t>character.asta.trace.01.trace-1</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -34776,12 +34776,12 @@
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -34825,11 +34825,11 @@
     </row>
     <row r="531">
       <c r="B531" t="n">
-        <v>22025</v>
+        <v>22022</v>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>character.asta.trace.05.trace-5</t>
+          <t>character.asta.trace.02.trace-2</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -34839,12 +34839,12 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -34888,11 +34888,11 @@
     </row>
     <row r="532">
       <c r="B532" t="n">
-        <v>22026</v>
+        <v>22023</v>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>character.asta.trace.06.sparks</t>
+          <t>character.asta.trace.03.trace-3</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
@@ -34902,12 +34902,12 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Sparks</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>火花</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -34951,11 +34951,11 @@
     </row>
     <row r="533">
       <c r="B533" t="n">
-        <v>22027</v>
+        <v>22024</v>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>character.asta.trace.07.ignite</t>
+          <t>character.asta.trace.04.trace-4</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -34965,12 +34965,12 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Ignite</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>点燃</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
@@ -35014,11 +35014,11 @@
     </row>
     <row r="534">
       <c r="B534" t="n">
-        <v>22028</v>
+        <v>22025</v>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>character.asta.trace.08.constellation</t>
+          <t>character.asta.trace.05.trace-5</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -35028,12 +35028,12 @@
       </c>
       <c r="E534" t="inlineStr">
         <is>
-          <t>Constellation</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>星座</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
@@ -35077,11 +35077,11 @@
     </row>
     <row r="535">
       <c r="B535" t="n">
-        <v>22029</v>
+        <v>22026</v>
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>character.asta.trace.09.dmg-boost-fire</t>
+          <t>character.asta.trace.06.sparks</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -35091,12 +35091,12 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>DMG Boost: Fire</t>
+          <t>Sparks</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>伤害强化•火</t>
+          <t>火花</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
@@ -35140,11 +35140,11 @@
     </row>
     <row r="536">
       <c r="B536" t="n">
-        <v>22030</v>
+        <v>22027</v>
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>character.asta.trace.10.def-boost</t>
+          <t>character.asta.trace.07.ignite</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -35154,12 +35154,12 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>DEF Boost</t>
+          <t>Ignite</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>防御强化</t>
+          <t>点燃</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
@@ -35203,11 +35203,11 @@
     </row>
     <row r="537">
       <c r="B537" t="n">
-        <v>22031</v>
+        <v>22028</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>character.asta.trace.11.dmg-boost-fire</t>
+          <t>character.asta.trace.08.constellation</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -35217,12 +35217,12 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>DMG Boost: Fire</t>
+          <t>Constellation</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>伤害强化•火</t>
+          <t>星座</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
@@ -35266,11 +35266,11 @@
     </row>
     <row r="538">
       <c r="B538" t="n">
-        <v>22032</v>
+        <v>22029</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>character.asta.trace.12.crit-rate-boost</t>
+          <t>character.asta.trace.09.dmg-boost-fire</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -35280,12 +35280,12 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost</t>
+          <t>DMG Boost: Fire</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>暴击率强化</t>
+          <t>伤害强化•火</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
@@ -35329,11 +35329,11 @@
     </row>
     <row r="539">
       <c r="B539" t="n">
-        <v>22033</v>
+        <v>22030</v>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>character.asta.trace.13.dmg-boost-fire</t>
+          <t>character.asta.trace.10.def-boost</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -35343,12 +35343,12 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>DMG Boost: Fire</t>
+          <t>DEF Boost</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>伤害强化•火</t>
+          <t>防御强化</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
@@ -35392,11 +35392,11 @@
     </row>
     <row r="540">
       <c r="B540" t="n">
-        <v>22034</v>
+        <v>22031</v>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>character.asta.trace.14.def-boost</t>
+          <t>character.asta.trace.11.dmg-boost-fire</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -35406,12 +35406,12 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>DEF Boost</t>
+          <t>DMG Boost: Fire</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>防御强化</t>
+          <t>伤害强化•火</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
@@ -35455,11 +35455,11 @@
     </row>
     <row r="541">
       <c r="B541" t="n">
-        <v>22035</v>
+        <v>22032</v>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>character.asta.trace.15.dmg-boost-fire</t>
+          <t>character.asta.trace.12.crit-rate-boost</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -35469,12 +35469,12 @@
       </c>
       <c r="E541" t="inlineStr">
         <is>
-          <t>DMG Boost: Fire</t>
+          <t>CRIT Rate Boost</t>
         </is>
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>伤害强化•火</t>
+          <t>暴击率强化</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
@@ -35518,11 +35518,11 @@
     </row>
     <row r="542">
       <c r="B542" t="n">
-        <v>22036</v>
+        <v>22033</v>
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>character.asta.trace.16.crit-rate-boost</t>
+          <t>character.asta.trace.13.dmg-boost-fire</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -35532,12 +35532,12 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost</t>
+          <t>DMG Boost: Fire</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>暴击率强化</t>
+          <t>伤害强化•火</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
@@ -35581,11 +35581,11 @@
     </row>
     <row r="543">
       <c r="B543" t="n">
-        <v>22037</v>
+        <v>22034</v>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>character.asta.trace.17.def-boost</t>
+          <t>character.asta.trace.14.def-boost</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -35644,11 +35644,11 @@
     </row>
     <row r="544">
       <c r="B544" t="n">
-        <v>22038</v>
+        <v>22035</v>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>character.asta.trace.18.dmg-boost-fire</t>
+          <t>character.asta.trace.15.dmg-boost-fire</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -35707,11 +35707,11 @@
     </row>
     <row r="545">
       <c r="B545" t="n">
-        <v>22039</v>
+        <v>22036</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>character.clara.trace.01.trace-1</t>
+          <t>character.asta.trace.16.crit-rate-boost</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -35721,12 +35721,12 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>CRIT Rate Boost</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>暴击率强化</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
@@ -35770,11 +35770,11 @@
     </row>
     <row r="546">
       <c r="B546" t="n">
-        <v>22040</v>
+        <v>22037</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>character.clara.trace.02.trace-2</t>
+          <t>character.asta.trace.17.def-boost</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -35784,12 +35784,12 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>DEF Boost</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>防御强化</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
@@ -35833,11 +35833,11 @@
     </row>
     <row r="547">
       <c r="B547" t="n">
-        <v>22041</v>
+        <v>22038</v>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>character.clara.trace.03.trace-3</t>
+          <t>character.asta.trace.18.dmg-boost-fire</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -35847,12 +35847,12 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>DMG Boost: Fire</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>伤害强化•火</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
@@ -35896,11 +35896,11 @@
     </row>
     <row r="548">
       <c r="B548" t="n">
-        <v>22042</v>
+        <v>22039</v>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>character.clara.trace.04.trace-4</t>
+          <t>character.clara.trace.01.trace-1</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -35910,12 +35910,12 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -35959,11 +35959,11 @@
     </row>
     <row r="549">
       <c r="B549" t="n">
-        <v>22043</v>
+        <v>22040</v>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>character.clara.trace.05.trace-5</t>
+          <t>character.clara.trace.02.trace-2</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -35973,12 +35973,12 @@
       </c>
       <c r="E549" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
@@ -36022,11 +36022,11 @@
     </row>
     <row r="550">
       <c r="B550" t="n">
-        <v>22044</v>
+        <v>22041</v>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>character.clara.trace.06.kinship</t>
+          <t>character.clara.trace.03.trace-3</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -36036,12 +36036,12 @@
       </c>
       <c r="E550" t="inlineStr">
         <is>
-          <t>Kinship</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>家人</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
@@ -36085,11 +36085,11 @@
     </row>
     <row r="551">
       <c r="B551" t="n">
-        <v>22045</v>
+        <v>22042</v>
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>character.clara.trace.07.under-protection</t>
+          <t>character.clara.trace.04.trace-4</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -36099,12 +36099,12 @@
       </c>
       <c r="E551" t="inlineStr">
         <is>
-          <t>Under Protection</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>守护</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
@@ -36148,11 +36148,11 @@
     </row>
     <row r="552">
       <c r="B552" t="n">
-        <v>22046</v>
+        <v>22043</v>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>character.clara.trace.08.revenge</t>
+          <t>character.clara.trace.05.trace-5</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -36162,12 +36162,12 @@
       </c>
       <c r="E552" t="inlineStr">
         <is>
-          <t>Revenge</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>复仇</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
@@ -36211,11 +36211,11 @@
     </row>
     <row r="553">
       <c r="B553" t="n">
-        <v>22047</v>
+        <v>22044</v>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>character.clara.trace.09.atk-boost</t>
+          <t>character.clara.trace.06.kinship</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -36225,12 +36225,12 @@
       </c>
       <c r="E553" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>Kinship</t>
         </is>
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>攻击强化</t>
+          <t>家人</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
@@ -36274,11 +36274,11 @@
     </row>
     <row r="554">
       <c r="B554" t="n">
-        <v>22048</v>
+        <v>22045</v>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>character.clara.trace.10.dmg-boost-physical</t>
+          <t>character.clara.trace.07.under-protection</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -36288,12 +36288,12 @@
       </c>
       <c r="E554" t="inlineStr">
         <is>
-          <t>DMG Boost: Physical</t>
+          <t>Under Protection</t>
         </is>
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>伤害强化•物理</t>
+          <t>守护</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
@@ -36337,11 +36337,11 @@
     </row>
     <row r="555">
       <c r="B555" t="n">
-        <v>22049</v>
+        <v>22046</v>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>character.clara.trace.11.atk-boost</t>
+          <t>character.clara.trace.08.revenge</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -36351,12 +36351,12 @@
       </c>
       <c r="E555" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>Revenge</t>
         </is>
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>攻击强化</t>
+          <t>复仇</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
@@ -36400,11 +36400,11 @@
     </row>
     <row r="556">
       <c r="B556" t="n">
-        <v>22050</v>
+        <v>22047</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>character.clara.trace.12.hp-boost</t>
+          <t>character.clara.trace.09.atk-boost</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -36414,12 +36414,12 @@
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>HP Boost</t>
+          <t>ATK Boost</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>生命强化</t>
+          <t>攻击强化</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
@@ -36463,11 +36463,11 @@
     </row>
     <row r="557">
       <c r="B557" t="n">
-        <v>22051</v>
+        <v>22048</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>character.clara.trace.13.atk-boost</t>
+          <t>character.clara.trace.10.dmg-boost-physical</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -36477,12 +36477,12 @@
       </c>
       <c r="E557" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>DMG Boost: Physical</t>
         </is>
       </c>
       <c r="F557" t="inlineStr">
         <is>
-          <t>攻击强化</t>
+          <t>伤害强化•物理</t>
         </is>
       </c>
       <c r="G557" t="inlineStr">
@@ -36526,11 +36526,11 @@
     </row>
     <row r="558">
       <c r="B558" t="n">
-        <v>22052</v>
+        <v>22049</v>
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>character.clara.trace.14.dmg-boost-physical</t>
+          <t>character.clara.trace.11.atk-boost</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -36540,12 +36540,12 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>DMG Boost: Physical</t>
+          <t>ATK Boost</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>伤害强化•物理</t>
+          <t>攻击强化</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -36589,11 +36589,11 @@
     </row>
     <row r="559">
       <c r="B559" t="n">
-        <v>22053</v>
+        <v>22050</v>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>character.clara.trace.15.atk-boost</t>
+          <t>character.clara.trace.12.hp-boost</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -36603,12 +36603,12 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>HP Boost</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>攻击强化</t>
+          <t>生命强化</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -36652,11 +36652,11 @@
     </row>
     <row r="560">
       <c r="B560" t="n">
-        <v>22054</v>
+        <v>22051</v>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>character.clara.trace.16.hp-boost</t>
+          <t>character.clara.trace.13.atk-boost</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -36666,12 +36666,12 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>HP Boost</t>
+          <t>ATK Boost</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>生命强化</t>
+          <t>攻击强化</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -36715,11 +36715,11 @@
     </row>
     <row r="561">
       <c r="B561" t="n">
-        <v>22055</v>
+        <v>22052</v>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>character.clara.trace.17.dmg-boost-physical</t>
+          <t>character.clara.trace.14.dmg-boost-physical</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -36778,11 +36778,11 @@
     </row>
     <row r="562">
       <c r="B562" t="n">
-        <v>22056</v>
+        <v>22053</v>
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>character.clara.trace.18.atk-boost</t>
+          <t>character.clara.trace.15.atk-boost</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -36841,11 +36841,11 @@
     </row>
     <row r="563">
       <c r="B563" t="n">
-        <v>22057</v>
+        <v>22054</v>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>character.firefly.trace.01.trace-1</t>
+          <t>character.clara.trace.16.hp-boost</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -36855,12 +36855,12 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>HP Boost</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>生命强化</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -36904,11 +36904,11 @@
     </row>
     <row r="564">
       <c r="B564" t="n">
-        <v>22058</v>
+        <v>22055</v>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>character.firefly.trace.02.trace-2</t>
+          <t>character.clara.trace.17.dmg-boost-physical</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
@@ -36918,12 +36918,12 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>DMG Boost: Physical</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>伤害强化•物理</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -36967,11 +36967,11 @@
     </row>
     <row r="565">
       <c r="B565" t="n">
-        <v>22059</v>
+        <v>22056</v>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>character.firefly.trace.03.trace-3</t>
+          <t>character.clara.trace.18.atk-boost</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -36981,12 +36981,12 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>ATK Boost</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>攻击强化</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -37030,11 +37030,11 @@
     </row>
     <row r="566">
       <c r="B566" t="n">
-        <v>22060</v>
+        <v>22057</v>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>character.firefly.trace.04.trace-4</t>
+          <t>character.firefly.trace.01.trace-1</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -37044,12 +37044,12 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="G566" t="inlineStr">
@@ -37093,11 +37093,11 @@
     </row>
     <row r="567">
       <c r="B567" t="n">
-        <v>22061</v>
+        <v>22058</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>character.firefly.trace.05.trace-5</t>
+          <t>character.firefly.trace.02.trace-2</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -37107,12 +37107,12 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -37156,11 +37156,11 @@
     </row>
     <row r="568">
       <c r="B568" t="n">
-        <v>22062</v>
+        <v>22059</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>character.firefly.trace.06.module-α-antilag-outburst</t>
+          <t>character.firefly.trace.03.trace-3</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -37170,12 +37170,12 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Module α: Antilag Outburst</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>α模组-偏时迸发</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
@@ -37219,11 +37219,11 @@
     </row>
     <row r="569">
       <c r="B569" t="n">
-        <v>22063</v>
+        <v>22060</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>character.firefly.trace.07.module-α-antilag-outburst</t>
+          <t>character.firefly.trace.04.trace-4</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -37233,12 +37233,12 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Module α: Antilag Outburst</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>α模组-偏时迸发</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
@@ -37282,11 +37282,11 @@
     </row>
     <row r="570">
       <c r="B570" t="n">
-        <v>22064</v>
+        <v>22061</v>
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>character.firefly.trace.08.module-β-autoreactive-armor</t>
+          <t>character.firefly.trace.05.trace-5</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -37296,12 +37296,12 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Module β: Autoreactive Armor</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>β模组-自限装甲</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -37345,11 +37345,11 @@
     </row>
     <row r="571">
       <c r="B571" t="n">
-        <v>22065</v>
+        <v>22062</v>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>character.firefly.trace.09.module-β-autoreactive-armor</t>
+          <t>character.firefly.trace.06.module-α-antilag-outburst</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -37359,12 +37359,12 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Module β: Autoreactive Armor</t>
+          <t>Module α: Antilag Outburst</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>β模组-自限装甲</t>
+          <t>α模组-偏时迸发</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -37408,11 +37408,11 @@
     </row>
     <row r="572">
       <c r="B572" t="n">
-        <v>22066</v>
+        <v>22063</v>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>character.firefly.trace.10.module-γ-core-overload</t>
+          <t>character.firefly.trace.07.module-α-antilag-outburst</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
@@ -37422,12 +37422,12 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Module γ: Core Overload</t>
+          <t>Module α: Antilag Outburst</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>γ模组-过载核心</t>
+          <t>α模组-偏时迸发</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -37471,11 +37471,11 @@
     </row>
     <row r="573">
       <c r="B573" t="n">
-        <v>22067</v>
+        <v>22064</v>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>character.firefly.trace.11.module-γ-core-overload</t>
+          <t>character.firefly.trace.08.module-β-autoreactive-armor</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
@@ -37485,12 +37485,12 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Module γ: Core Overload</t>
+          <t>Module β: Autoreactive Armor</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>γ模组-过载核心</t>
+          <t>β模组-自限装甲</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
@@ -37534,11 +37534,11 @@
     </row>
     <row r="574">
       <c r="B574" t="n">
-        <v>22068</v>
+        <v>22065</v>
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>character.firefly.trace.12.break-boost</t>
+          <t>character.firefly.trace.09.module-β-autoreactive-armor</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -37548,12 +37548,12 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Break Boost</t>
+          <t>Module β: Autoreactive Armor</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>击破强化</t>
+          <t>β模组-自限装甲</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
@@ -37597,11 +37597,11 @@
     </row>
     <row r="575">
       <c r="B575" t="n">
-        <v>22069</v>
+        <v>22066</v>
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>character.firefly.trace.13.effect-res-boost</t>
+          <t>character.firefly.trace.10.module-γ-core-overload</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -37611,12 +37611,12 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Effect RES Boost</t>
+          <t>Module γ: Core Overload</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>效果抵抗强化</t>
+          <t>γ模组-过载核心</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
@@ -37660,11 +37660,11 @@
     </row>
     <row r="576">
       <c r="B576" t="n">
-        <v>22070</v>
+        <v>22067</v>
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>character.firefly.trace.14.break-boost</t>
+          <t>character.firefly.trace.11.module-γ-core-overload</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -37674,12 +37674,12 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Break Boost</t>
+          <t>Module γ: Core Overload</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>击破强化</t>
+          <t>γ模组-过载核心</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -37723,11 +37723,11 @@
     </row>
     <row r="577">
       <c r="B577" t="n">
-        <v>22071</v>
+        <v>22068</v>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>character.firefly.trace.15.spd-boost</t>
+          <t>character.firefly.trace.12.break-boost</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -37737,12 +37737,12 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>SPD Boost</t>
+          <t>Break Boost</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>速度强化</t>
+          <t>击破强化</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -37786,11 +37786,11 @@
     </row>
     <row r="578">
       <c r="B578" t="n">
-        <v>22072</v>
+        <v>22069</v>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>character.firefly.trace.16.break-boost</t>
+          <t>character.firefly.trace.13.effect-res-boost</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -37800,12 +37800,12 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Break Boost</t>
+          <t>Effect RES Boost</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>击破强化</t>
+          <t>效果抵抗强化</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -37849,11 +37849,11 @@
     </row>
     <row r="579">
       <c r="B579" t="n">
-        <v>22073</v>
+        <v>22070</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>character.firefly.trace.17.effect-res-boost</t>
+          <t>character.firefly.trace.14.break-boost</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -37863,12 +37863,12 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Effect RES Boost</t>
+          <t>Break Boost</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>效果抵抗强化</t>
+          <t>击破强化</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
@@ -37912,11 +37912,11 @@
     </row>
     <row r="580">
       <c r="B580" t="n">
-        <v>22074</v>
+        <v>22071</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>character.firefly.trace.18.break-boost</t>
+          <t>character.firefly.trace.15.spd-boost</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -37926,12 +37926,12 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Break Boost</t>
+          <t>SPD Boost</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>击破强化</t>
+          <t>速度强化</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -37975,11 +37975,11 @@
     </row>
     <row r="581">
       <c r="B581" t="n">
-        <v>22075</v>
+        <v>22072</v>
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>character.firefly.trace.19.spd-boost</t>
+          <t>character.firefly.trace.16.break-boost</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -37989,12 +37989,12 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>SPD Boost</t>
+          <t>Break Boost</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>速度强化</t>
+          <t>击破强化</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -38038,11 +38038,11 @@
     </row>
     <row r="582">
       <c r="B582" t="n">
-        <v>22076</v>
+        <v>22073</v>
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>character.firefly.trace.20.effect-res-boost</t>
+          <t>character.firefly.trace.17.effect-res-boost</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -38101,11 +38101,11 @@
     </row>
     <row r="583">
       <c r="B583" t="n">
-        <v>22077</v>
+        <v>22074</v>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>character.firefly.trace.21.break-boost</t>
+          <t>character.firefly.trace.18.break-boost</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -38164,11 +38164,11 @@
     </row>
     <row r="584">
       <c r="B584" t="n">
-        <v>22078</v>
+        <v>22075</v>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>character.kafka.trace.01.trace-1</t>
+          <t>character.firefly.trace.19.spd-boost</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -38178,12 +38178,12 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>SPD Boost</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>速度强化</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -38227,11 +38227,11 @@
     </row>
     <row r="585">
       <c r="B585" t="n">
-        <v>22079</v>
+        <v>22076</v>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>character.kafka.trace.02.trace-2</t>
+          <t>character.firefly.trace.20.effect-res-boost</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -38241,12 +38241,12 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>Effect RES Boost</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>效果抵抗强化</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
@@ -38290,11 +38290,11 @@
     </row>
     <row r="586">
       <c r="B586" t="n">
-        <v>22080</v>
+        <v>22077</v>
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>character.kafka.trace.03.trace-3</t>
+          <t>character.firefly.trace.21.break-boost</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -38304,12 +38304,12 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>Break Boost</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>击破强化</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -38353,11 +38353,11 @@
     </row>
     <row r="587">
       <c r="B587" t="n">
-        <v>22081</v>
+        <v>22078</v>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>character.kafka.trace.04.trace-4</t>
+          <t>character.kafka.trace.01.trace-1</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -38367,12 +38367,12 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -38416,11 +38416,11 @@
     </row>
     <row r="588">
       <c r="B588" t="n">
-        <v>22082</v>
+        <v>22079</v>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>character.kafka.trace.05.trace-5</t>
+          <t>character.kafka.trace.02.trace-2</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
@@ -38430,12 +38430,12 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -38479,11 +38479,11 @@
     </row>
     <row r="589">
       <c r="B589" t="n">
-        <v>22083</v>
+        <v>22080</v>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>character.kafka.trace.06.torture</t>
+          <t>character.kafka.trace.03.trace-3</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -38493,12 +38493,12 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Torture</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>折磨</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
@@ -38542,11 +38542,11 @@
     </row>
     <row r="590">
       <c r="B590" t="n">
-        <v>22084</v>
+        <v>22081</v>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>character.kafka.trace.07.torture</t>
+          <t>character.kafka.trace.04.trace-4</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -38556,12 +38556,12 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Torture</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>折磨</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
@@ -38605,11 +38605,11 @@
     </row>
     <row r="591">
       <c r="B591" t="n">
-        <v>22085</v>
+        <v>22082</v>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>character.kafka.trace.08.plunder</t>
+          <t>character.kafka.trace.05.trace-5</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -38619,12 +38619,12 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Plunder</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
         <is>
-          <t>掠夺</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="G591" t="inlineStr">
@@ -38668,11 +38668,11 @@
     </row>
     <row r="592">
       <c r="B592" t="n">
-        <v>22086</v>
+        <v>22083</v>
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>character.kafka.trace.09.plunder</t>
+          <t>character.kafka.trace.06.torture</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -38682,12 +38682,12 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Plunder</t>
+          <t>Torture</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>掠夺</t>
+          <t>折磨</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
@@ -38731,11 +38731,11 @@
     </row>
     <row r="593">
       <c r="B593" t="n">
-        <v>22087</v>
+        <v>22084</v>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>character.kafka.trace.10.thorns</t>
+          <t>character.kafka.trace.07.torture</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -38745,12 +38745,12 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Thorns</t>
+          <t>Torture</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>荆棘</t>
+          <t>折磨</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
@@ -38794,11 +38794,11 @@
     </row>
     <row r="594">
       <c r="B594" t="n">
-        <v>22088</v>
+        <v>22085</v>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>character.kafka.trace.11.atk-boost</t>
+          <t>character.kafka.trace.08.plunder</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -38808,12 +38808,12 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>Plunder</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>攻击强化</t>
+          <t>掠夺</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
@@ -38857,11 +38857,11 @@
     </row>
     <row r="595">
       <c r="B595" t="n">
-        <v>22089</v>
+        <v>22086</v>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>character.kafka.trace.12.effect-hit-rate-boost</t>
+          <t>character.kafka.trace.09.plunder</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -38871,12 +38871,12 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Effect Hit Rate Boost</t>
+          <t>Plunder</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>效果命中强化</t>
+          <t>掠夺</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
@@ -38920,11 +38920,11 @@
     </row>
     <row r="596">
       <c r="B596" t="n">
-        <v>22090</v>
+        <v>22087</v>
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>character.kafka.trace.13.atk-boost</t>
+          <t>character.kafka.trace.10.thorns</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -38934,12 +38934,12 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>Thorns</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>攻击强化</t>
+          <t>荆棘</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
@@ -38983,11 +38983,11 @@
     </row>
     <row r="597">
       <c r="B597" t="n">
-        <v>22091</v>
+        <v>22088</v>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>character.kafka.trace.14.hp-boost</t>
+          <t>character.kafka.trace.11.atk-boost</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -38997,12 +38997,12 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>HP Boost</t>
+          <t>ATK Boost</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>生命强化</t>
+          <t>攻击强化</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
@@ -39046,11 +39046,11 @@
     </row>
     <row r="598">
       <c r="B598" t="n">
-        <v>22092</v>
+        <v>22089</v>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>character.kafka.trace.15.atk-boost</t>
+          <t>character.kafka.trace.12.effect-hit-rate-boost</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -39060,12 +39060,12 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>Effect Hit Rate Boost</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>攻击强化</t>
+          <t>效果命中强化</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -39109,11 +39109,11 @@
     </row>
     <row r="599">
       <c r="B599" t="n">
-        <v>22093</v>
+        <v>22090</v>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>character.kafka.trace.16.effect-hit-rate-boost</t>
+          <t>character.kafka.trace.13.atk-boost</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -39123,12 +39123,12 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Effect Hit Rate Boost</t>
+          <t>ATK Boost</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>效果命中强化</t>
+          <t>攻击强化</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
@@ -39172,11 +39172,11 @@
     </row>
     <row r="600">
       <c r="B600" t="n">
-        <v>22094</v>
+        <v>22091</v>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>character.kafka.trace.17.atk-boost</t>
+          <t>character.kafka.trace.14.hp-boost</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -39186,12 +39186,12 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>ATK Boost</t>
+          <t>HP Boost</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>攻击强化</t>
+          <t>生命强化</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -39235,11 +39235,11 @@
     </row>
     <row r="601">
       <c r="B601" t="n">
-        <v>22095</v>
+        <v>22092</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>character.kafka.trace.18.hp-boost</t>
+          <t>character.kafka.trace.15.atk-boost</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -39249,12 +39249,12 @@
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>HP Boost</t>
+          <t>ATK Boost</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>生命强化</t>
+          <t>攻击强化</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
@@ -39298,11 +39298,11 @@
     </row>
     <row r="602">
       <c r="B602" t="n">
-        <v>22096</v>
+        <v>22093</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>character.kafka.trace.19.effect-hit-rate-boost</t>
+          <t>character.kafka.trace.16.effect-hit-rate-boost</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -39361,11 +39361,11 @@
     </row>
     <row r="603">
       <c r="B603" t="n">
-        <v>22097</v>
+        <v>22094</v>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>character.kafka.trace.20.atk-boost</t>
+          <t>character.kafka.trace.17.atk-boost</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -39424,11 +39424,11 @@
     </row>
     <row r="604">
       <c r="B604" t="n">
-        <v>22098</v>
+        <v>22095</v>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.01.trace-1</t>
+          <t>character.kafka.trace.18.hp-boost</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -39438,12 +39438,12 @@
       </c>
       <c r="E604" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>HP Boost</t>
         </is>
       </c>
       <c r="F604" t="inlineStr">
         <is>
-          <t>Trace 1</t>
+          <t>生命强化</t>
         </is>
       </c>
       <c r="G604" t="inlineStr">
@@ -39487,11 +39487,11 @@
     </row>
     <row r="605">
       <c r="B605" t="n">
-        <v>22099</v>
+        <v>22096</v>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.02.trace-2</t>
+          <t>character.kafka.trace.19.effect-hit-rate-boost</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -39501,12 +39501,12 @@
       </c>
       <c r="E605" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>Effect Hit Rate Boost</t>
         </is>
       </c>
       <c r="F605" t="inlineStr">
         <is>
-          <t>Trace 2</t>
+          <t>效果命中强化</t>
         </is>
       </c>
       <c r="G605" t="inlineStr">
@@ -39550,11 +39550,11 @@
     </row>
     <row r="606">
       <c r="B606" t="n">
-        <v>22100</v>
+        <v>22097</v>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.03.trace-3</t>
+          <t>character.kafka.trace.20.atk-boost</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -39564,12 +39564,12 @@
       </c>
       <c r="E606" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>ATK Boost</t>
         </is>
       </c>
       <c r="F606" t="inlineStr">
         <is>
-          <t>Trace 3</t>
+          <t>攻击强化</t>
         </is>
       </c>
       <c r="G606" t="inlineStr">
@@ -39613,11 +39613,11 @@
     </row>
     <row r="607">
       <c r="B607" t="n">
-        <v>22101</v>
+        <v>22098</v>
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.04.trace-4</t>
+          <t>character.silver-wolf-lv-999.trace.01.trace-1</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -39627,12 +39627,12 @@
       </c>
       <c r="E607" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="F607" t="inlineStr">
         <is>
-          <t>Trace 4</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="G607" t="inlineStr">
@@ -39676,11 +39676,11 @@
     </row>
     <row r="608">
       <c r="B608" t="n">
-        <v>22102</v>
+        <v>22099</v>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.05.trace-5</t>
+          <t>character.silver-wolf-lv-999.trace.02.trace-2</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -39690,12 +39690,12 @@
       </c>
       <c r="E608" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="F608" t="inlineStr">
         <is>
-          <t>Trace 5</t>
+          <t>Trace 2</t>
         </is>
       </c>
       <c r="G608" t="inlineStr">
@@ -39739,11 +39739,11 @@
     </row>
     <row r="609">
       <c r="B609" t="n">
-        <v>22103</v>
+        <v>22100</v>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.06.false-ending-speedrun</t>
+          <t>character.silver-wolf-lv-999.trace.03.trace-3</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -39753,12 +39753,12 @@
       </c>
       <c r="E609" t="inlineStr">
         <is>
-          <t>False Ending Speedrun</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="F609" t="inlineStr">
         <is>
-          <t>假结局速通攻略</t>
+          <t>Trace 3</t>
         </is>
       </c>
       <c r="G609" t="inlineStr">
@@ -39802,11 +39802,11 @@
     </row>
     <row r="610">
       <c r="B610" t="n">
-        <v>22104</v>
+        <v>22101</v>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.07.true-ending-unlocked</t>
+          <t>character.silver-wolf-lv-999.trace.04.trace-4</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -39816,12 +39816,12 @@
       </c>
       <c r="E610" t="inlineStr">
         <is>
-          <t>True Ending Unlocked</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="F610" t="inlineStr">
         <is>
-          <t>真结局解锁条件</t>
+          <t>Trace 4</t>
         </is>
       </c>
       <c r="G610" t="inlineStr">
@@ -39865,11 +39865,11 @@
     </row>
     <row r="611">
       <c r="B611" t="n">
-        <v>22105</v>
+        <v>22102</v>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.08.secret-level-maxed</t>
+          <t>character.silver-wolf-lv-999.trace.05.trace-5</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -39879,12 +39879,12 @@
       </c>
       <c r="E611" t="inlineStr">
         <is>
-          <t>Secret Level Maxed</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="F611" t="inlineStr">
         <is>
-          <t>隐藏关卡全成就</t>
+          <t>Trace 5</t>
         </is>
       </c>
       <c r="G611" t="inlineStr">
@@ -39928,11 +39928,11 @@
     </row>
     <row r="612">
       <c r="B612" t="n">
-        <v>22106</v>
+        <v>22103</v>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.09.crit-rate-boost</t>
+          <t>character.silver-wolf-lv-999.trace.06.false-ending-speedrun</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -39942,12 +39942,12 @@
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost</t>
+          <t>False Ending Speedrun</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>暴击率强化</t>
+          <t>假结局速通攻略</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
@@ -39991,11 +39991,11 @@
     </row>
     <row r="613">
       <c r="B613" t="n">
-        <v>22107</v>
+        <v>22104</v>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.10.spd-boost</t>
+          <t>character.silver-wolf-lv-999.trace.07.true-ending-unlocked</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -40005,12 +40005,12 @@
       </c>
       <c r="E613" t="inlineStr">
         <is>
-          <t>SPD Boost</t>
+          <t>True Ending Unlocked</t>
         </is>
       </c>
       <c r="F613" t="inlineStr">
         <is>
-          <t>速度强化</t>
+          <t>真结局解锁条件</t>
         </is>
       </c>
       <c r="G613" t="inlineStr">
@@ -40054,11 +40054,11 @@
     </row>
     <row r="614">
       <c r="B614" t="n">
-        <v>22108</v>
+        <v>22105</v>
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.11.crit-rate-boost</t>
+          <t>character.silver-wolf-lv-999.trace.08.secret-level-maxed</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -40068,12 +40068,12 @@
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost</t>
+          <t>Secret Level Maxed</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>暴击率强化</t>
+          <t>隐藏关卡全成就</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -40117,11 +40117,11 @@
     </row>
     <row r="615">
       <c r="B615" t="n">
-        <v>22109</v>
+        <v>22106</v>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.12.elation-boost</t>
+          <t>character.silver-wolf-lv-999.trace.09.crit-rate-boost</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -40131,12 +40131,12 @@
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Elation Boost</t>
+          <t>CRIT Rate Boost</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>欢愉度强化</t>
+          <t>暴击率强化</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -40180,11 +40180,11 @@
     </row>
     <row r="616">
       <c r="B616" t="n">
-        <v>22110</v>
+        <v>22107</v>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.13.crit-rate-boost</t>
+          <t>character.silver-wolf-lv-999.trace.10.spd-boost</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
@@ -40194,12 +40194,12 @@
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost</t>
+          <t>SPD Boost</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>暴击率强化</t>
+          <t>速度强化</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -40243,11 +40243,11 @@
     </row>
     <row r="617">
       <c r="B617" t="n">
-        <v>22111</v>
+        <v>22108</v>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.14.spd-boost</t>
+          <t>character.silver-wolf-lv-999.trace.11.crit-rate-boost</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
@@ -40257,12 +40257,12 @@
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>SPD Boost</t>
+          <t>CRIT Rate Boost</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>速度强化</t>
+          <t>暴击率强化</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
@@ -40306,11 +40306,11 @@
     </row>
     <row r="618">
       <c r="B618" t="n">
-        <v>22112</v>
+        <v>22109</v>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.15.crit-rate-boost</t>
+          <t>character.silver-wolf-lv-999.trace.12.elation-boost</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -40320,12 +40320,12 @@
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost</t>
+          <t>Elation Boost</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>暴击率强化</t>
+          <t>欢愉度强化</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
@@ -40369,11 +40369,11 @@
     </row>
     <row r="619">
       <c r="B619" t="n">
-        <v>22113</v>
+        <v>22110</v>
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.16.elation-boost</t>
+          <t>character.silver-wolf-lv-999.trace.13.crit-rate-boost</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -40383,12 +40383,12 @@
       </c>
       <c r="E619" t="inlineStr">
         <is>
-          <t>Elation Boost</t>
+          <t>CRIT Rate Boost</t>
         </is>
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>欢愉度强化</t>
+          <t>暴击率强化</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -40432,11 +40432,11 @@
     </row>
     <row r="620">
       <c r="B620" t="n">
-        <v>22114</v>
+        <v>22111</v>
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.17.spd-boost</t>
+          <t>character.silver-wolf-lv-999.trace.14.spd-boost</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -40495,11 +40495,11 @@
     </row>
     <row r="621">
       <c r="B621" t="n">
-        <v>22115</v>
+        <v>22112</v>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.18.crit-rate-boost</t>
+          <t>character.silver-wolf-lv-999.trace.15.crit-rate-boost</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -40558,11 +40558,11 @@
     </row>
     <row r="622">
       <c r="B622" t="n">
-        <v>22116</v>
+        <v>22113</v>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.trace.19.elation-skill</t>
+          <t>character.silver-wolf-lv-999.trace.16.elation-boost</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -40572,12 +40572,12 @@
       </c>
       <c r="E622" t="inlineStr">
         <is>
-          <t>Elation Skill</t>
+          <t>Elation Boost</t>
         </is>
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>欢愉技</t>
+          <t>欢愉度强化</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -40621,31 +40621,31 @@
     </row>
     <row r="623">
       <c r="B623" t="n">
-        <v>23001</v>
+        <v>22114</v>
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>character.aglaea.eidolon.1</t>
+          <t>character.silver-wolf-lv-999.trace.17.spd-boost</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
         <is>
-          <t>Eidolon</t>
+          <t>Trace</t>
         </is>
       </c>
       <c r="E623" t="inlineStr">
         <is>
-          <t>Drift at the Whim of Venus</t>
+          <t>SPD Boost</t>
         </is>
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>飘曳金星的行列</t>
+          <t>速度强化</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
         <is>
-          <t>Complete E1-E6 rank identity and exact prepared ability-level patches.</t>
+          <t>Complete battle-relevant Trace identity, graph edge and prepared mechanic payload.</t>
         </is>
       </c>
       <c r="H623" t="inlineStr">
@@ -40684,31 +40684,31 @@
     </row>
     <row r="624">
       <c r="B624" t="n">
-        <v>23002</v>
+        <v>22115</v>
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>character.aglaea.eidolon.2</t>
+          <t>character.silver-wolf-lv-999.trace.18.crit-rate-boost</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
         <is>
-          <t>Eidolon</t>
+          <t>Trace</t>
         </is>
       </c>
       <c r="E624" t="inlineStr">
         <is>
-          <t>Sail on the Raft of Eyelids</t>
+          <t>CRIT Rate Boost</t>
         </is>
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>行舟命运的眼睑</t>
+          <t>暴击率强化</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
         <is>
-          <t>Complete E1-E6 rank identity and exact prepared ability-level patches.</t>
+          <t>Complete battle-relevant Trace identity, graph edge and prepared mechanic payload.</t>
         </is>
       </c>
       <c r="H624" t="inlineStr">
@@ -40747,31 +40747,31 @@
     </row>
     <row r="625">
       <c r="B625" t="n">
-        <v>23003</v>
+        <v>22116</v>
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>character.aglaea.eidolon.3</t>
+          <t>character.silver-wolf-lv-999.trace.19.elation-skill</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
         <is>
-          <t>Eidolon</t>
+          <t>Trace</t>
         </is>
       </c>
       <c r="E625" t="inlineStr">
         <is>
-          <t>Bequeath in the Coalescence of Dew</t>
+          <t>Elation Skill</t>
         </is>
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>华珠凝滞的礼物</t>
+          <t>欢愉技</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
         <is>
-          <t>Complete E1-E6 rank identity and exact prepared ability-level patches.</t>
+          <t>Complete battle-relevant Trace identity, graph edge and prepared mechanic payload.</t>
         </is>
       </c>
       <c r="H625" t="inlineStr">
@@ -40810,11 +40810,11 @@
     </row>
     <row r="626">
       <c r="B626" t="n">
-        <v>23004</v>
+        <v>23001</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>character.aglaea.eidolon.4</t>
+          <t>character.aglaea.eidolon.1</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -40824,12 +40824,12 @@
       </c>
       <c r="E626" t="inlineStr">
         <is>
-          <t>Flicker Below the Surface of Marble</t>
+          <t>Drift at the Whim of Venus</t>
         </is>
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>大理石内的闪烁</t>
+          <t>飘曳金星的行列</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -40873,11 +40873,11 @@
     </row>
     <row r="627">
       <c r="B627" t="n">
-        <v>23005</v>
+        <v>23002</v>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>character.aglaea.eidolon.5</t>
+          <t>character.aglaea.eidolon.2</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -40887,12 +40887,12 @@
       </c>
       <c r="E627" t="inlineStr">
         <is>
-          <t>Weave Under the Shroud of Woe</t>
+          <t>Sail on the Raft of Eyelids</t>
         </is>
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>漆黑苦难的织者</t>
+          <t>行舟命运的眼睑</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -40936,11 +40936,11 @@
     </row>
     <row r="628">
       <c r="B628" t="n">
-        <v>23006</v>
+        <v>23003</v>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>character.aglaea.eidolon.6</t>
+          <t>character.aglaea.eidolon.3</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -40950,12 +40950,12 @@
       </c>
       <c r="E628" t="inlineStr">
         <is>
-          <t>Fluctuate in the Tapestry of Fates</t>
+          <t>Bequeath in the Coalescence of Dew</t>
         </is>
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>盈虚无常的金线</t>
+          <t>华珠凝滞的礼物</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -40999,11 +40999,11 @@
     </row>
     <row r="629">
       <c r="B629" t="n">
-        <v>23007</v>
+        <v>23004</v>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>character.asta.eidolon.1</t>
+          <t>character.aglaea.eidolon.4</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -41013,12 +41013,12 @@
       </c>
       <c r="E629" t="inlineStr">
         <is>
-          <t>Star Sings Sans Verses or Vocals</t>
+          <t>Flicker Below the Surface of Marble</t>
         </is>
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>星有无言之歌</t>
+          <t>大理石内的闪烁</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -41062,11 +41062,11 @@
     </row>
     <row r="630">
       <c r="B630" t="n">
-        <v>23008</v>
+        <v>23005</v>
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>character.asta.eidolon.2</t>
+          <t>character.aglaea.eidolon.5</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -41076,12 +41076,12 @@
       </c>
       <c r="E630" t="inlineStr">
         <is>
-          <t>Moon Speaks in Wax and Wane</t>
+          <t>Weave Under the Shroud of Woe</t>
         </is>
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>月见圆缺之意</t>
+          <t>漆黑苦难的织者</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -41125,11 +41125,11 @@
     </row>
     <row r="631">
       <c r="B631" t="n">
-        <v>23009</v>
+        <v>23006</v>
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>character.asta.eidolon.3</t>
+          <t>character.aglaea.eidolon.6</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -41139,12 +41139,12 @@
       </c>
       <c r="E631" t="inlineStr">
         <is>
-          <t>Meteor Showers for Wish and Want</t>
+          <t>Fluctuate in the Tapestry of Fates</t>
         </is>
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>黄道陨石之变</t>
+          <t>盈虚无常的金线</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -41188,11 +41188,11 @@
     </row>
     <row r="632">
       <c r="B632" t="n">
-        <v>23010</v>
+        <v>23007</v>
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>character.asta.eidolon.4</t>
+          <t>character.asta.eidolon.1</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -41202,12 +41202,12 @@
       </c>
       <c r="E632" t="inlineStr">
         <is>
-          <t>Aurora Basks in Beauty and Bliss</t>
+          <t>Star Sings Sans Verses or Vocals</t>
         </is>
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>极光显现之时</t>
+          <t>星有无言之歌</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -41251,11 +41251,11 @@
     </row>
     <row r="633">
       <c r="B633" t="n">
-        <v>23011</v>
+        <v>23008</v>
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>character.asta.eidolon.5</t>
+          <t>character.asta.eidolon.2</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -41265,12 +41265,12 @@
       </c>
       <c r="E633" t="inlineStr">
         <is>
-          <t>Nebula Secludes in Runes and Riddles</t>
+          <t>Moon Speaks in Wax and Wane</t>
         </is>
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>深空天体之谜</t>
+          <t>月见圆缺之意</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -41314,11 +41314,11 @@
     </row>
     <row r="634">
       <c r="B634" t="n">
-        <v>23012</v>
+        <v>23009</v>
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>character.asta.eidolon.6</t>
+          <t>character.asta.eidolon.3</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -41328,12 +41328,12 @@
       </c>
       <c r="E634" t="inlineStr">
         <is>
-          <t>Cosmos Dreams in Calm and Comfort</t>
+          <t>Meteor Showers for Wish and Want</t>
         </is>
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>眠于银河之下</t>
+          <t>黄道陨石之变</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -41377,11 +41377,11 @@
     </row>
     <row r="635">
       <c r="B635" t="n">
-        <v>23013</v>
+        <v>23010</v>
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>character.clara.eidolon.1</t>
+          <t>character.asta.eidolon.4</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -41391,12 +41391,12 @@
       </c>
       <c r="E635" t="inlineStr">
         <is>
-          <t>A Tall Figure</t>
+          <t>Aurora Basks in Beauty and Bliss</t>
         </is>
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>高大的背影</t>
+          <t>极光显现之时</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -41440,11 +41440,11 @@
     </row>
     <row r="636">
       <c r="B636" t="n">
-        <v>23014</v>
+        <v>23011</v>
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>character.clara.eidolon.2</t>
+          <t>character.asta.eidolon.5</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -41454,12 +41454,12 @@
       </c>
       <c r="E636" t="inlineStr">
         <is>
-          <t>A Tight Embrace</t>
+          <t>Nebula Secludes in Runes and Riddles</t>
         </is>
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>紧紧的拥抱</t>
+          <t>深空天体之谜</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -41503,11 +41503,11 @@
     </row>
     <row r="637">
       <c r="B637" t="n">
-        <v>23015</v>
+        <v>23012</v>
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>character.clara.eidolon.3</t>
+          <t>character.asta.eidolon.6</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -41517,12 +41517,12 @@
       </c>
       <c r="E637" t="inlineStr">
         <is>
-          <t>Cold Steel Armor</t>
+          <t>Cosmos Dreams in Calm and Comfort</t>
         </is>
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>冰冷的钢甲</t>
+          <t>眠于银河之下</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -41566,11 +41566,11 @@
     </row>
     <row r="638">
       <c r="B638" t="n">
-        <v>23016</v>
+        <v>23013</v>
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>character.clara.eidolon.4</t>
+          <t>character.clara.eidolon.1</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -41580,12 +41580,12 @@
       </c>
       <c r="E638" t="inlineStr">
         <is>
-          <t>Family's Warmth</t>
+          <t>A Tall Figure</t>
         </is>
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>家人的温暖</t>
+          <t>高大的背影</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -41629,11 +41629,11 @@
     </row>
     <row r="639">
       <c r="B639" t="n">
-        <v>23017</v>
+        <v>23014</v>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>character.clara.eidolon.5</t>
+          <t>character.clara.eidolon.2</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -41643,12 +41643,12 @@
       </c>
       <c r="E639" t="inlineStr">
         <is>
-          <t>A Small Promise</t>
+          <t>A Tight Embrace</t>
         </is>
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>小小的承诺</t>
+          <t>紧紧的拥抱</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -41692,11 +41692,11 @@
     </row>
     <row r="640">
       <c r="B640" t="n">
-        <v>23018</v>
+        <v>23015</v>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>character.clara.eidolon.6</t>
+          <t>character.clara.eidolon.3</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -41706,12 +41706,12 @@
       </c>
       <c r="E640" t="inlineStr">
         <is>
-          <t>Long Company</t>
+          <t>Cold Steel Armor</t>
         </is>
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>长久的陪伴</t>
+          <t>冰冷的钢甲</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -41755,11 +41755,11 @@
     </row>
     <row r="641">
       <c r="B641" t="n">
-        <v>23019</v>
+        <v>23016</v>
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>character.firefly.eidolon.1</t>
+          <t>character.clara.eidolon.4</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -41769,12 +41769,12 @@
       </c>
       <c r="E641" t="inlineStr">
         <is>
-          <t>In Reddened Chrysalis, I Once Rest</t>
+          <t>Family's Warmth</t>
         </is>
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>我曾安眠，赤染之茧</t>
+          <t>家人的温暖</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -41818,11 +41818,11 @@
     </row>
     <row r="642">
       <c r="B642" t="n">
-        <v>23020</v>
+        <v>23017</v>
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>character.firefly.eidolon.2</t>
+          <t>character.clara.eidolon.5</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -41832,12 +41832,12 @@
       </c>
       <c r="E642" t="inlineStr">
         <is>
-          <t>From Shattered Sky, I Free Fall</t>
+          <t>A Small Promise</t>
         </is>
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>自破碎的天空坠落</t>
+          <t>小小的承诺</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -41881,11 +41881,11 @@
     </row>
     <row r="643">
       <c r="B643" t="n">
-        <v>23021</v>
+        <v>23018</v>
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>character.firefly.eidolon.3</t>
+          <t>character.clara.eidolon.6</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -41895,12 +41895,12 @@
       </c>
       <c r="E643" t="inlineStr">
         <is>
-          <t>Amidst Silenced Stars, I Deep Sleep</t>
+          <t>Long Company</t>
         </is>
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>沉睡在静默的星河</t>
+          <t>长久的陪伴</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -41944,11 +41944,11 @@
     </row>
     <row r="644">
       <c r="B644" t="n">
-        <v>23022</v>
+        <v>23019</v>
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>character.firefly.eidolon.4</t>
+          <t>character.firefly.eidolon.1</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -41958,12 +41958,12 @@
       </c>
       <c r="E644" t="inlineStr">
         <is>
-          <t>Upon Lighted Fyrefly, I Soon Gaze</t>
+          <t>In Reddened Chrysalis, I Once Rest</t>
         </is>
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>我会看见，飞萤之火</t>
+          <t>我曾安眠，赤染之茧</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -42007,11 +42007,11 @@
     </row>
     <row r="645">
       <c r="B645" t="n">
-        <v>23023</v>
+        <v>23020</v>
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>character.firefly.eidolon.5</t>
+          <t>character.firefly.eidolon.2</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -42021,12 +42021,12 @@
       </c>
       <c r="E645" t="inlineStr">
         <is>
-          <t>From Undreamt Night, I Thence Shine</t>
+          <t>From Shattered Sky, I Free Fall</t>
         </is>
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>自无梦的长夜亮起</t>
+          <t>自破碎的天空坠落</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -42070,11 +42070,11 @@
     </row>
     <row r="646">
       <c r="B646" t="n">
-        <v>23024</v>
+        <v>23021</v>
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>character.firefly.eidolon.6</t>
+          <t>character.firefly.eidolon.3</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -42084,12 +42084,12 @@
       </c>
       <c r="E646" t="inlineStr">
         <is>
-          <t>In Finalized Morrow, I Full Bloom</t>
+          <t>Amidst Silenced Stars, I Deep Sleep</t>
         </is>
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>绽放在终竟的明天</t>
+          <t>沉睡在静默的星河</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -42133,11 +42133,11 @@
     </row>
     <row r="647">
       <c r="B647" t="n">
-        <v>23025</v>
+        <v>23022</v>
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>character.kafka.eidolon.1</t>
+          <t>character.firefly.eidolon.4</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -42147,12 +42147,12 @@
       </c>
       <c r="E647" t="inlineStr">
         <is>
-          <t>Da Capo</t>
+          <t>Upon Lighted Fyrefly, I Soon Gaze</t>
         </is>
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>无穷动！无穷</t>
+          <t>我会看见，飞萤之火</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -42196,11 +42196,11 @@
     </row>
     <row r="648">
       <c r="B648" t="n">
-        <v>23026</v>
+        <v>23023</v>
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>character.kafka.eidolon.2</t>
+          <t>character.firefly.eidolon.5</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -42210,12 +42210,12 @@
       </c>
       <c r="E648" t="inlineStr">
         <is>
-          <t>Fortississimo</t>
+          <t>From Undreamt Night, I Thence Shine</t>
         </is>
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>狂想者，呜咽</t>
+          <t>自无梦的长夜亮起</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -42259,11 +42259,11 @@
     </row>
     <row r="649">
       <c r="B649" t="n">
-        <v>23027</v>
+        <v>23024</v>
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>character.kafka.eidolon.3</t>
+          <t>character.firefly.eidolon.6</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -42273,12 +42273,12 @@
       </c>
       <c r="E649" t="inlineStr">
         <is>
-          <t>Capriccio</t>
+          <t>In Finalized Morrow, I Full Bloom</t>
         </is>
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>我赞美，即兴</t>
+          <t>绽放在终竟的明天</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -42322,11 +42322,11 @@
     </row>
     <row r="650">
       <c r="B650" t="n">
-        <v>23028</v>
+        <v>23025</v>
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>character.kafka.eidolon.4</t>
+          <t>character.kafka.eidolon.1</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -42336,12 +42336,12 @@
       </c>
       <c r="E650" t="inlineStr">
         <is>
-          <t>Recitativo</t>
+          <t>Da Capo</t>
         </is>
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>把宣叙呈献给</t>
+          <t>无穷动！无穷</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -42385,11 +42385,11 @@
     </row>
     <row r="651">
       <c r="B651" t="n">
-        <v>23029</v>
+        <v>23026</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>character.kafka.eidolon.5</t>
+          <t>character.kafka.eidolon.2</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -42399,12 +42399,12 @@
       </c>
       <c r="E651" t="inlineStr">
         <is>
-          <t>Doloroso</t>
+          <t>Fortississimo</t>
         </is>
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>只有今晚奏鸣</t>
+          <t>狂想者，呜咽</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -42448,11 +42448,11 @@
     </row>
     <row r="652">
       <c r="B652" t="n">
-        <v>23030</v>
+        <v>23027</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>character.kafka.eidolon.6</t>
+          <t>character.kafka.eidolon.3</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -42462,12 +42462,12 @@
       </c>
       <c r="E652" t="inlineStr">
         <is>
-          <t>Leggiero</t>
+          <t>Capriccio</t>
         </is>
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>回旋，悄悄地</t>
+          <t>我赞美，即兴</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -42511,11 +42511,11 @@
     </row>
     <row r="653">
       <c r="B653" t="n">
-        <v>23031</v>
+        <v>23028</v>
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.eidolon.1</t>
+          <t>character.kafka.eidolon.4</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -42525,12 +42525,12 @@
       </c>
       <c r="E653" t="inlineStr">
         <is>
-          <t>Aether Editing: Eidolon +1</t>
+          <t>Recitativo</t>
         </is>
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>以太编辑：星魂+1</t>
+          <t>把宣叙呈献给</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -42574,11 +42574,11 @@
     </row>
     <row r="654">
       <c r="B654" t="n">
-        <v>23032</v>
+        <v>23029</v>
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.eidolon.2</t>
+          <t>character.kafka.eidolon.5</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -42588,12 +42588,12 @@
       </c>
       <c r="E654" t="inlineStr">
         <is>
-          <t>It's a Feature, Not a Bug</t>
+          <t>Doloroso</t>
         </is>
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>是机制，不是BUG</t>
+          <t>只有今晚奏鸣</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -42637,11 +42637,11 @@
     </row>
     <row r="655">
       <c r="B655" t="n">
-        <v>23033</v>
+        <v>23030</v>
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.eidolon.3</t>
+          <t>character.kafka.eidolon.6</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -42651,12 +42651,12 @@
       </c>
       <c r="E655" t="inlineStr">
         <is>
-          <t>Max Lv. 15? Says who?</t>
+          <t>Leggiero</t>
         </is>
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>只有15级？谁填的</t>
+          <t>回旋，悄悄地</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -42700,11 +42700,11 @@
     </row>
     <row r="656">
       <c r="B656" t="n">
-        <v>23034</v>
+        <v>23031</v>
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.eidolon.4</t>
+          <t>character.silver-wolf-lv-999.eidolon.1</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -42714,12 +42714,12 @@
       </c>
       <c r="E656" t="inlineStr">
         <is>
-          <t>I Came. I Saw. I One-Shot.</t>
+          <t>Aether Editing: Eidolon +1</t>
         </is>
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>我来，我见，我..秒了</t>
+          <t>以太编辑：星魂+1</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -42763,11 +42763,11 @@
     </row>
     <row r="657">
       <c r="B657" t="n">
-        <v>23035</v>
+        <v>23032</v>
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.eidolon.5</t>
+          <t>character.silver-wolf-lv-999.eidolon.2</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -42777,12 +42777,12 @@
       </c>
       <c r="E657" t="inlineStr">
         <is>
-          <t>Basic ATK Is the New Ultimate</t>
+          <t>It's a Feature, Not a Bug</t>
         </is>
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>平A即是大招</t>
+          <t>是机制，不是BUG</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -42826,11 +42826,11 @@
     </row>
     <row r="658">
       <c r="B658" t="n">
-        <v>23036</v>
+        <v>23033</v>
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>character.silver-wolf-lv-999.eidolon.6</t>
+          <t>character.silver-wolf-lv-999.eidolon.3</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -42840,12 +42840,12 @@
       </c>
       <c r="E658" t="inlineStr">
         <is>
-          <t>Solo Maxxing!</t>
+          <t>Max Lv. 15? Says who?</t>
         </is>
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>我独自满级！</t>
+          <t>只有15级？谁填的</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -42889,41 +42889,41 @@
     </row>
     <row r="659">
       <c r="B659" t="n">
-        <v>24002</v>
+        <v>23034</v>
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>program.v1b.asta.astrometry.rule</t>
+          <t>character.silver-wolf-lv-999.eidolon.4</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Eidolon</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
         <is>
-          <t>Asta Charging Rule</t>
+          <t>I Came. I Saw. I One-Shot.</t>
         </is>
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>艾丝妲蓄能规则</t>
+          <t>我来，我见，我..秒了</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>Production Rule IR owner for the Charging stack probe.</t>
+          <t>Complete E1-E6 rank identity and exact prepared ability-level patches.</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>蓄能层数探针的生产规则 IR 所有者。</t>
+          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J659" t="inlineStr">
@@ -42952,41 +42952,41 @@
     </row>
     <row r="660">
       <c r="B660" t="n">
-        <v>24003</v>
+        <v>23035</v>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>program.v1b.asta.charging.slot</t>
+          <t>character.silver-wolf-lv-999.eidolon.5</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
         <is>
-          <t>StateSlot</t>
+          <t>Eidolon</t>
         </is>
       </c>
       <c r="E660" t="inlineStr">
         <is>
-          <t>Asta Charging Slot</t>
+          <t>Basic ATK Is the New Ultimate</t>
         </is>
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>艾丝妲蓄能槽位</t>
+          <t>平A即是大招</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>Production bounded stack input for dynamic aura evaluation.</t>
+          <t>Complete E1-E6 rank identity and exact prepared ability-level patches.</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
         <is>
-          <t>动态光环求值的生产有界层数输入。</t>
+          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
         </is>
       </c>
       <c r="I660" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J660" t="inlineStr">
@@ -43015,41 +43015,41 @@
     </row>
     <row r="661">
       <c r="B661" t="n">
-        <v>24004</v>
+        <v>23036</v>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>program.v1b.asta.team-atk.modifier</t>
+          <t>character.silver-wolf-lv-999.eidolon.6</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>Eidolon</t>
         </is>
       </c>
       <c r="E661" t="inlineStr">
         <is>
-          <t>Asta Team ATK Modifier</t>
+          <t>Solo Maxxing!</t>
         </is>
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>艾丝妲全队攻击修正</t>
+          <t>我独自满级！</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>Production dynamic ATK modifier compiled from the released stack relation.</t>
+          <t>Complete E1-E6 rank identity and exact prepared ability-level patches.</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>由已发布层数关系编译的生产动态攻击修正。</t>
+          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J661" t="inlineStr">
@@ -43078,36 +43078,36 @@
     </row>
     <row r="662">
       <c r="B662" t="n">
-        <v>24006</v>
+        <v>24002</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>program.v1b.asta.astral-blessing.spd-effect</t>
+          <t>program.v1b.asta.astrometry.rule</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Effect</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E662" t="inlineStr">
         <is>
-          <t>Asta Astral Blessing SPD Effect</t>
+          <t>Asta Charging Rule</t>
         </is>
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>艾丝妲星空祝言速度效果</t>
+          <t>艾丝妲蓄能规则</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
         <is>
-          <t>Production two-turn team SPD effect with an independent target-turn clock.</t>
+          <t>Production Rule IR owner for the Charging stack probe.</t>
         </is>
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>具有独立目标回合时钟的生产两回合全队速度效果。</t>
+          <t>蓄能层数探针的生产规则 IR 所有者。</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -43141,36 +43141,36 @@
     </row>
     <row r="663">
       <c r="B663" t="n">
-        <v>24007</v>
+        <v>24003</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>program.v1b.asta.astral-blessing.program</t>
+          <t>program.v1b.asta.charging.slot</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>StateSlot</t>
         </is>
       </c>
       <c r="E663" t="inlineStr">
         <is>
-          <t>Asta Astral Blessing Program</t>
+          <t>Asta Charging Slot</t>
         </is>
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>艾丝妲星空祝言程序</t>
+          <t>艾丝妲蓄能槽位</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
         <is>
-          <t>Production Rule IR program applying the authored duration effect.</t>
+          <t>Production bounded stack input for dynamic aura evaluation.</t>
         </is>
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t>应用已编写持续时间效果的生产规则 IR 程序。</t>
+          <t>动态光环求值的生产有界层数输入。</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -43204,41 +43204,41 @@
     </row>
     <row r="664">
       <c r="B664" t="n">
-        <v>24051</v>
+        <v>24004</v>
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>selector.v1b.asta-modifier.1</t>
+          <t>program.v1b.asta.team-atk.modifier</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Modifier</t>
         </is>
       </c>
       <c r="E664" t="inlineStr">
         <is>
-          <t>Asta Modifier Selector 1</t>
+          <t>Asta Team ATK Modifier</t>
         </is>
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>Asta Modifier选择器1</t>
+          <t>艾丝妲全队攻击修正</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Production dynamic ATK modifier compiled from the released stack relation.</t>
         </is>
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>由已发布层数关系编译的生产动态攻击修正。</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J664" t="inlineStr">
@@ -43267,41 +43267,41 @@
     </row>
     <row r="665">
       <c r="B665" t="n">
-        <v>24052</v>
+        <v>24006</v>
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>selector.v1b.asta-modifier.2</t>
+          <t>program.v1b.asta.astral-blessing.spd-effect</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="E665" t="inlineStr">
         <is>
-          <t>Asta Modifier Selector 2</t>
+          <t>Asta Astral Blessing SPD Effect</t>
         </is>
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>Asta Modifier选择器2</t>
+          <t>艾丝妲星空祝言速度效果</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Production two-turn team SPD effect with an independent target-turn clock.</t>
         </is>
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>具有独立目标回合时钟的生产两回合全队速度效果。</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J665" t="inlineStr">
@@ -43330,41 +43330,41 @@
     </row>
     <row r="666">
       <c r="B666" t="n">
-        <v>24053</v>
+        <v>24007</v>
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>selector.v1b.asta-modifier.3</t>
+          <t>program.v1b.asta.astral-blessing.program</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E666" t="inlineStr">
         <is>
-          <t>Asta Modifier Selector 3</t>
+          <t>Asta Astral Blessing Program</t>
         </is>
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>Asta Modifier选择器3</t>
+          <t>艾丝妲星空祝言程序</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Production Rule IR program applying the authored duration effect.</t>
         </is>
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>应用已编写持续时间效果的生产规则 IR 程序。</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J666" t="inlineStr">
@@ -43393,41 +43393,41 @@
     </row>
     <row r="667">
       <c r="B667" t="n">
-        <v>24104</v>
+        <v>24051</v>
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>program.v1b.kafka.shock.effect</t>
+          <t>selector.v1b.asta-modifier.1</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
         <is>
-          <t>Effect</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E667" t="inlineStr">
         <is>
-          <t>Kafka Shock Effect</t>
+          <t>Asta Modifier Selector 1</t>
         </is>
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>卡芙卡触电效果</t>
+          <t>Asta Modifier选择器1</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
         <is>
-          <t>Production retained two-turn Lightning DoT definition.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t>生产保留的两回合雷属性持续伤害定义。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J667" t="inlineStr">
@@ -43456,41 +43456,41 @@
     </row>
     <row r="668">
       <c r="B668" t="n">
-        <v>24105</v>
+        <v>24052</v>
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>program.v1b.kafka.skill.program</t>
+          <t>selector.v1b.asta-modifier.2</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E668" t="inlineStr">
         <is>
-          <t>Kafka Skill Program</t>
+          <t>Asta Modifier Selector 2</t>
         </is>
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>卡芙卡战技程序</t>
+          <t>Asta Modifier选择器2</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
         <is>
-          <t>Primary-target 75 percent DoT detonation program.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>主目标百分之七十五持续伤害引爆程序。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J668" t="inlineStr">
@@ -43519,41 +43519,41 @@
     </row>
     <row r="669">
       <c r="B669" t="n">
-        <v>24106</v>
+        <v>24053</v>
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>program.v1b.kafka.ultimate.program</t>
+          <t>selector.v1b.asta-modifier.3</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E669" t="inlineStr">
         <is>
-          <t>Kafka Ultimate Program</t>
+          <t>Asta Modifier Selector 3</t>
         </is>
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>卡芙卡终结技程序</t>
+          <t>Asta Modifier选择器3</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
         <is>
-          <t>All-target Shock and full DoT detonation program.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t>全目标触电与完整持续伤害引爆程序。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J669" t="inlineStr">
@@ -43582,36 +43582,36 @@
     </row>
     <row r="670">
       <c r="B670" t="n">
-        <v>24107</v>
+        <v>24104</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>program.v1b.kafka.follow-up.program</t>
+          <t>program.v1b.kafka.shock.effect</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="E670" t="inlineStr">
         <is>
-          <t>Kafka Follow-up Program</t>
+          <t>Kafka Shock Effect</t>
         </is>
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>卡芙卡追加攻击程序</t>
+          <t>卡芙卡触电效果</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
         <is>
-          <t>Ordered follow-up damage then Shock application program.</t>
+          <t>Production retained two-turn Lightning DoT definition.</t>
         </is>
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>依次造成追加攻击伤害并施加触电的程序。</t>
+          <t>生产保留的两回合雷属性持续伤害定义。</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -43645,36 +43645,36 @@
     </row>
     <row r="671">
       <c r="B671" t="n">
-        <v>24108</v>
+        <v>24105</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>program.v1b.kafka.follow-up.rule</t>
+          <t>program.v1b.kafka.skill.program</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E671" t="inlineStr">
         <is>
-          <t>Kafka Follow-up Rule</t>
+          <t>Kafka Skill Program</t>
         </is>
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>卡芙卡追加攻击规则</t>
+          <t>卡芙卡战技程序</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
         <is>
-          <t>Turn-scoped follow-up owner with typed reset state.</t>
+          <t>Primary-target 75 percent DoT detonation program.</t>
         </is>
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t>具有类型化回合重置状态的追加攻击规则所有者。</t>
+          <t>主目标百分之七十五持续伤害引爆程序。</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -43708,36 +43708,36 @@
     </row>
     <row r="672">
       <c r="B672" t="n">
-        <v>24109</v>
+        <v>24106</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>program.v1b.kafka.follow-up.used.slot</t>
+          <t>program.v1b.kafka.ultimate.program</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>StateSlot</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E672" t="inlineStr">
         <is>
-          <t>Kafka Follow-up Used Slot</t>
+          <t>Kafka Ultimate Program</t>
         </is>
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>卡芙卡追加攻击已用槽位</t>
+          <t>卡芙卡终结技程序</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
         <is>
-          <t>Production bounded once-per-owner-turn state.</t>
+          <t>All-target Shock and full DoT detonation program.</t>
         </is>
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t>生产的每所有者回合一次有界状态。</t>
+          <t>全目标触电与完整持续伤害引爆程序。</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -43771,41 +43771,41 @@
     </row>
     <row r="673">
       <c r="B673" t="n">
-        <v>24151</v>
+        <v>24107</v>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>selector.v1b.kafka-dot.1</t>
+          <t>program.v1b.kafka.follow-up.program</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E673" t="inlineStr">
         <is>
-          <t>Kafka Dot Selector 1</t>
+          <t>Kafka Follow-up Program</t>
         </is>
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>Kafka Dot选择器1</t>
+          <t>卡芙卡追加攻击程序</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Ordered follow-up damage then Shock application program.</t>
         </is>
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>依次造成追加攻击伤害并施加触电的程序。</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="J673" t="inlineStr">
@@ -43834,41 +43834,41 @@
     </row>
     <row r="674">
       <c r="B674" t="n">
-        <v>24152</v>
+        <v>24108</v>
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>selector.v1b.kafka-dot.2</t>
+          <t>program.v1b.kafka.follow-up.rule</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E674" t="inlineStr">
         <is>
-          <t>Kafka Dot Selector 2</t>
+          <t>Kafka Follow-up Rule</t>
         </is>
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>Kafka Dot选择器2</t>
+          <t>卡芙卡追加攻击规则</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Turn-scoped follow-up owner with typed reset state.</t>
         </is>
       </c>
       <c r="H674" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>具有类型化回合重置状态的追加攻击规则所有者。</t>
         </is>
       </c>
       <c r="I674" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="J674" t="inlineStr">
@@ -43897,41 +43897,41 @@
     </row>
     <row r="675">
       <c r="B675" t="n">
-        <v>24153</v>
+        <v>24109</v>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>selector.v1b.kafka-dot.3</t>
+          <t>program.v1b.kafka.follow-up.used.slot</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>StateSlot</t>
         </is>
       </c>
       <c r="E675" t="inlineStr">
         <is>
-          <t>Kafka Dot Selector 3</t>
+          <t>Kafka Follow-up Used Slot</t>
         </is>
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>Kafka Dot选择器3</t>
+          <t>卡芙卡追加攻击已用槽位</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Production bounded once-per-owner-turn state.</t>
         </is>
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>生产的每所有者回合一次有界状态。</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="J675" t="inlineStr">
@@ -43960,41 +43960,41 @@
     </row>
     <row r="676">
       <c r="B676" t="n">
-        <v>24201</v>
+        <v>24151</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>program.v1b.clara.because-were-family.source</t>
+          <t>selector.v1b.kafka-dot.1</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Ability</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E676" t="inlineStr">
         <is>
-          <t>Clara Talent Counter</t>
+          <t>Kafka Dot Selector 1</t>
         </is>
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>克拉拉天赋反击</t>
+          <t>Kafka Dot选择器1</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
         <is>
-          <t>Production queued counter ability constrained by the released Talent record.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>由已发布天赋记录约束的生产排队反击能力。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J676" t="inlineStr">
@@ -44023,41 +44023,41 @@
     </row>
     <row r="677">
       <c r="B677" t="n">
-        <v>24204</v>
+        <v>24152</v>
       </c>
       <c r="C677" t="inlineStr">
         <is>
-          <t>program.v1b.clara.counter.program</t>
+          <t>selector.v1b.kafka-dot.2</t>
         </is>
       </c>
       <c r="D677" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E677" t="inlineStr">
         <is>
-          <t>Clara Counter Queue Program</t>
+          <t>Kafka Dot Selector 2</t>
         </is>
       </c>
       <c r="F677" t="inlineStr">
         <is>
-          <t>克拉拉反击队列程序</t>
+          <t>Kafka Dot选择器2</t>
         </is>
       </c>
       <c r="G677" t="inlineStr">
         <is>
-          <t>Queues the counter and consumes one shared charge in authored order.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>按编写顺序排入反击并消耗一次共享次数。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J677" t="inlineStr">
@@ -44086,41 +44086,41 @@
     </row>
     <row r="678">
       <c r="B678" t="n">
-        <v>24205</v>
+        <v>24153</v>
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>program.v1b.clara.counter.rule</t>
+          <t>selector.v1b.kafka-dot.3</t>
         </is>
       </c>
       <c r="D678" t="inlineStr">
         <is>
-          <t>Rule</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E678" t="inlineStr">
         <is>
-          <t>Clara Counter Trigger Rule</t>
+          <t>Kafka Dot Selector 3</t>
         </is>
       </c>
       <c r="F678" t="inlineStr">
         <is>
-          <t>克拉拉反击触发规则</t>
+          <t>Kafka Dot选择器3</t>
         </is>
       </c>
       <c r="G678" t="inlineStr">
         <is>
-          <t>Hit-bound rule retaining explicit priority and once-key scope.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>保留显式优先级与一次性键作用域的命中规则。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J678" t="inlineStr">
@@ -44149,36 +44149,36 @@
     </row>
     <row r="679">
       <c r="B679" t="n">
-        <v>24206</v>
+        <v>24201</v>
       </c>
       <c r="C679" t="inlineStr">
         <is>
-          <t>program.v1b.clara.enhanced-charges.slot</t>
+          <t>program.v1b.clara.because-were-family.source</t>
         </is>
       </c>
       <c r="D679" t="inlineStr">
         <is>
-          <t>StateSlot</t>
+          <t>Ability</t>
         </is>
       </c>
       <c r="E679" t="inlineStr">
         <is>
-          <t>Clara Enhanced Counter Charges</t>
+          <t>Clara Talent Counter</t>
         </is>
       </c>
       <c r="F679" t="inlineStr">
         <is>
-          <t>克拉拉强化反击次数</t>
+          <t>克拉拉天赋反击</t>
         </is>
       </c>
       <c r="G679" t="inlineStr">
         <is>
-          <t>Clara-owned bounded shared charge state initialized to two.</t>
+          <t>Production queued counter ability constrained by the released Talent record.</t>
         </is>
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t>由克拉拉持有且初始为二的有界共享次数状态。</t>
+          <t>由已发布天赋记录约束的生产排队反击能力。</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -44212,41 +44212,41 @@
     </row>
     <row r="680">
       <c r="B680" t="n">
-        <v>24251</v>
+        <v>24204</v>
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>selector.v1b.clara-counter.1</t>
+          <t>program.v1b.clara.counter.program</t>
         </is>
       </c>
       <c r="D680" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E680" t="inlineStr">
         <is>
-          <t>Clara Counter Selector 1</t>
+          <t>Clara Counter Queue Program</t>
         </is>
       </c>
       <c r="F680" t="inlineStr">
         <is>
-          <t>Clara Counter选择器1</t>
+          <t>克拉拉反击队列程序</t>
         </is>
       </c>
       <c r="G680" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Queues the counter and consumes one shared charge in authored order.</t>
         </is>
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>按编写顺序排入反击并消耗一次共享次数。</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J680" t="inlineStr">
@@ -44275,41 +44275,41 @@
     </row>
     <row r="681">
       <c r="B681" t="n">
-        <v>24252</v>
+        <v>24205</v>
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>selector.v1b.clara-counter.2</t>
+          <t>program.v1b.clara.counter.rule</t>
         </is>
       </c>
       <c r="D681" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Rule</t>
         </is>
       </c>
       <c r="E681" t="inlineStr">
         <is>
-          <t>Clara Counter Selector 2</t>
+          <t>Clara Counter Trigger Rule</t>
         </is>
       </c>
       <c r="F681" t="inlineStr">
         <is>
-          <t>Clara Counter选择器2</t>
+          <t>克拉拉反击触发规则</t>
         </is>
       </c>
       <c r="G681" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Hit-bound rule retaining explicit priority and once-key scope.</t>
         </is>
       </c>
       <c r="H681" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>保留显式优先级与一次性键作用域的命中规则。</t>
         </is>
       </c>
       <c r="I681" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J681" t="inlineStr">
@@ -44338,41 +44338,41 @@
     </row>
     <row r="682">
       <c r="B682" t="n">
-        <v>24303</v>
+        <v>24206</v>
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>program.v1b.firefly.normal-skill.program</t>
+          <t>program.v1b.clara.enhanced-charges.slot</t>
         </is>
       </c>
       <c r="D682" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>StateSlot</t>
         </is>
       </c>
       <c r="E682" t="inlineStr">
         <is>
-          <t>Firefly HP Damage Program</t>
+          <t>Clara Enhanced Counter Charges</t>
         </is>
       </c>
       <c r="F682" t="inlineStr">
         <is>
-          <t>流萤生命伤害程序</t>
+          <t>克拉拉强化反击次数</t>
         </is>
       </c>
       <c r="G682" t="inlineStr">
         <is>
-          <t>Ordered HP consumption Energy restoration and damage Rule IR program.</t>
+          <t>Clara-owned bounded shared charge state initialized to two.</t>
         </is>
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t>按序执行生命消耗能量恢复和伤害的规则程序。</t>
+          <t>由克拉拉持有且初始为二的有界共享次数状态。</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="J682" t="inlineStr">
@@ -44401,41 +44401,41 @@
     </row>
     <row r="683">
       <c r="B683" t="n">
-        <v>24304</v>
+        <v>24251</v>
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>program.v1b.firefly.ultimate.program</t>
+          <t>selector.v1b.clara-counter.1</t>
         </is>
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E683" t="inlineStr">
         <is>
-          <t>Firefly Ultimate Order Program</t>
+          <t>Clara Counter Selector 1</t>
         </is>
       </c>
       <c r="F683" t="inlineStr">
         <is>
-          <t>流萤终结技顺序程序</t>
+          <t>Clara Counter选择器1</t>
         </is>
       </c>
       <c r="G683" t="inlineStr">
         <is>
-          <t>Ordered countdown RedMode action advance and Energy reset Rule IR program.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>按序执行倒计时红温模式行动提前和能量重置的规则程序。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J683" t="inlineStr">
@@ -44464,41 +44464,41 @@
     </row>
     <row r="684">
       <c r="B684" t="n">
-        <v>24305</v>
+        <v>24252</v>
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>program.v1b.firefly.redmode.effect</t>
+          <t>selector.v1b.clara-counter.2</t>
         </is>
       </c>
       <c r="D684" t="inlineStr">
         <is>
-          <t>Effect</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E684" t="inlineStr">
         <is>
-          <t>Firefly RedMode Effect</t>
+          <t>Clara Counter Selector 2</t>
         </is>
       </c>
       <c r="F684" t="inlineStr">
         <is>
-          <t>流萤红温模式效果</t>
+          <t>Clara Counter选择器2</t>
         </is>
       </c>
       <c r="G684" t="inlineStr">
         <is>
-          <t>Production effect identity representing Complete Combustion ownership.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>代表完全燃烧所有权的生产效果标识。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J684" t="inlineStr">
@@ -44527,11 +44527,11 @@
     </row>
     <row r="685">
       <c r="B685" t="n">
-        <v>24308</v>
+        <v>24303</v>
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>program.v1b.firefly.break.program</t>
+          <t>program.v1b.firefly.normal-skill.program</t>
         </is>
       </c>
       <c r="D685" t="inlineStr">
@@ -44541,22 +44541,22 @@
       </c>
       <c r="E685" t="inlineStr">
         <is>
-          <t>Firefly Weakness Toughness Super Break</t>
+          <t>Firefly HP Damage Program</t>
         </is>
       </c>
       <c r="F685" t="inlineStr">
         <is>
-          <t>流萤弱点击破超击破程序</t>
+          <t>流萤生命伤害程序</t>
         </is>
       </c>
       <c r="G685" t="inlineStr">
         <is>
-          <t>Ordered Fire Weakness Toughness reduction and Super Break Rule IR program.</t>
+          <t>Ordered HP consumption Energy restoration and damage Rule IR program.</t>
         </is>
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>按序执行火弱点韧性削减与超击破的规则程序。</t>
+          <t>按序执行生命消耗能量恢复和伤害的规则程序。</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -44590,36 +44590,36 @@
     </row>
     <row r="686">
       <c r="B686" t="n">
-        <v>24309</v>
+        <v>24304</v>
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>program.v1b.firefly.complete-combustion-countdown</t>
+          <t>program.v1b.firefly.ultimate.program</t>
         </is>
       </c>
       <c r="D686" t="inlineStr">
         <is>
-          <t>Ability</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E686" t="inlineStr">
         <is>
-          <t>Complete Combustion Countdown</t>
+          <t>Firefly Ultimate Order Program</t>
         </is>
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>完全燃烧倒计时</t>
+          <t>流萤终结技顺序程序</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
         <is>
-          <t>Production timeline-only transformation-ending action.</t>
+          <t>Ordered countdown RedMode action advance and Energy reset Rule IR program.</t>
         </is>
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>生产的时间线专用变身结束行动。</t>
+          <t>按序执行倒计时红温模式行动提前和能量重置的规则程序。</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -44653,41 +44653,41 @@
     </row>
     <row r="687">
       <c r="B687" t="n">
-        <v>24351</v>
+        <v>24305</v>
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>selector.v1b.firefly-damage.1</t>
+          <t>program.v1b.firefly.redmode.effect</t>
         </is>
       </c>
       <c r="D687" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Effect</t>
         </is>
       </c>
       <c r="E687" t="inlineStr">
         <is>
-          <t>Firefly Damage Selector 1</t>
+          <t>Firefly RedMode Effect</t>
         </is>
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>Firefly Damage选择器1</t>
+          <t>流萤红温模式效果</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Production effect identity representing Complete Combustion ownership.</t>
         </is>
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>代表完全燃烧所有权的生产效果标识。</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J687" t="inlineStr">
@@ -44716,41 +44716,41 @@
     </row>
     <row r="688">
       <c r="B688" t="n">
-        <v>24352</v>
+        <v>24308</v>
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>selector.v1b.firefly-damage.2</t>
+          <t>program.v1b.firefly.break.program</t>
         </is>
       </c>
       <c r="D688" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E688" t="inlineStr">
         <is>
-          <t>Firefly Damage Selector 2</t>
+          <t>Firefly Weakness Toughness Super Break</t>
         </is>
       </c>
       <c r="F688" t="inlineStr">
         <is>
-          <t>Firefly Damage选择器2</t>
+          <t>流萤弱点击破超击破程序</t>
         </is>
       </c>
       <c r="G688" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Ordered Fire Weakness Toughness reduction and Super Break Rule IR program.</t>
         </is>
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>按序执行火弱点韧性削减与超击破的规则程序。</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J688" t="inlineStr">
@@ -44779,36 +44779,36 @@
     </row>
     <row r="689">
       <c r="B689" t="n">
-        <v>24402</v>
+        <v>24309</v>
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>program.v1b.firefly-transform.complete-combustion.form</t>
+          <t>program.v1b.firefly.complete-combustion-countdown</t>
         </is>
       </c>
       <c r="D689" t="inlineStr">
         <is>
-          <t>CharacterForm</t>
+          <t>Ability</t>
         </is>
       </c>
       <c r="E689" t="inlineStr">
         <is>
-          <t>Firefly Complete Combustion Form</t>
+          <t>Complete Combustion Countdown</t>
         </is>
       </c>
       <c r="F689" t="inlineStr">
         <is>
-          <t>流萤完全燃烧形态</t>
+          <t>完全燃烧倒计时</t>
         </is>
       </c>
       <c r="G689" t="inlineStr">
         <is>
-          <t>Production replacement-form identity constrained by Complete Combustion.</t>
+          <t>Production timeline-only transformation-ending action.</t>
         </is>
       </c>
       <c r="H689" t="inlineStr">
         <is>
-          <t>由完全燃烧约束的生产替换形态标识。</t>
+          <t>生产的时间线专用变身结束行动。</t>
         </is>
       </c>
       <c r="I689" t="inlineStr">
@@ -44842,41 +44842,41 @@
     </row>
     <row r="690">
       <c r="B690" t="n">
-        <v>24405</v>
+        <v>24351</v>
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>program.v1b.firefly-transform.program</t>
+          <t>selector.v1b.firefly-damage.1</t>
         </is>
       </c>
       <c r="D690" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E690" t="inlineStr">
         <is>
-          <t>Firefly Transformation Program</t>
+          <t>Firefly Damage Selector 1</t>
         </is>
       </c>
       <c r="F690" t="inlineStr">
         <is>
-          <t>流萤变身程序</t>
+          <t>Firefly Damage选择器1</t>
         </is>
       </c>
       <c r="G690" t="inlineStr">
         <is>
-          <t>Orders form replacement ability replacement and transformed presence.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>按序执行形态替换能力替换与变身在场状态。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J690" t="inlineStr">
@@ -44905,11 +44905,11 @@
     </row>
     <row r="691">
       <c r="B691" t="n">
-        <v>24451</v>
+        <v>24352</v>
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>selector.v1b.firefly-transform.1</t>
+          <t>selector.v1b.firefly-damage.2</t>
         </is>
       </c>
       <c r="D691" t="inlineStr">
@@ -44919,12 +44919,12 @@
       </c>
       <c r="E691" t="inlineStr">
         <is>
-          <t>Firefly Transform Selector 1</t>
+          <t>Firefly Damage Selector 2</t>
         </is>
       </c>
       <c r="F691" t="inlineStr">
         <is>
-          <t>Firefly Transform选择器1</t>
+          <t>Firefly Damage选择器2</t>
         </is>
       </c>
       <c r="G691" t="inlineStr">
@@ -44968,11 +44968,11 @@
     </row>
     <row r="692">
       <c r="B692" t="n">
-        <v>24505</v>
+        <v>24402</v>
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>program.v1b.aglaea.garmentmaker.form</t>
+          <t>program.v1b.firefly-transform.complete-combustion.form</t>
         </is>
       </c>
       <c r="D692" t="inlineStr">
@@ -44982,27 +44982,27 @@
       </c>
       <c r="E692" t="inlineStr">
         <is>
-          <t>Garmentmaker Memosprite Form</t>
+          <t>Firefly Complete Combustion Form</t>
         </is>
       </c>
       <c r="F692" t="inlineStr">
         <is>
-          <t>衣匠忆灵形态</t>
+          <t>流萤完全燃烧形态</t>
         </is>
       </c>
       <c r="G692" t="inlineStr">
         <is>
-          <t>Production linked-form identity owned by the Aglaea fixture.</t>
+          <t>Production replacement-form identity constrained by Complete Combustion.</t>
         </is>
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t>由阿格莱雅探针拥有的生产链接形态标识。</t>
+          <t>由完全燃烧约束的生产替换形态标识。</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J692" t="inlineStr">
@@ -45031,11 +45031,11 @@
     </row>
     <row r="693">
       <c r="B693" t="n">
-        <v>24506</v>
+        <v>24405</v>
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>program.v1b.aglaea.memosprite.program</t>
+          <t>program.v1b.firefly-transform.program</t>
         </is>
       </c>
       <c r="D693" t="inlineStr">
@@ -45045,27 +45045,27 @@
       </c>
       <c r="E693" t="inlineStr">
         <is>
-          <t>Aglaea Memosprite Lifecycle</t>
+          <t>Firefly Transformation Program</t>
         </is>
       </c>
       <c r="F693" t="inlineStr">
         <is>
-          <t>阿格莱雅忆灵生命周期</t>
+          <t>流萤变身程序</t>
         </is>
       </c>
       <c r="G693" t="inlineStr">
         <is>
-          <t>Orders memosprite spawn linked presence and explicit departure.</t>
+          <t>Orders form replacement ability replacement and transformed presence.</t>
         </is>
       </c>
       <c r="H693" t="inlineStr">
         <is>
-          <t>按序执行忆灵生成链接在场与显式退场。</t>
+          <t>按序执行形态替换能力替换与变身在场状态。</t>
         </is>
       </c>
       <c r="I693" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J693" t="inlineStr">
@@ -45094,41 +45094,41 @@
     </row>
     <row r="694">
       <c r="B694" t="n">
-        <v>24507</v>
+        <v>24451</v>
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>program.v1b.aglaea.garmentmaker-action</t>
+          <t>selector.v1b.firefly-transform.1</t>
         </is>
       </c>
       <c r="D694" t="inlineStr">
         <is>
-          <t>Ability</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E694" t="inlineStr">
         <is>
-          <t>Garmentmaker Action</t>
+          <t>Firefly Transform Selector 1</t>
         </is>
       </c>
       <c r="F694" t="inlineStr">
         <is>
-          <t>衣匠行动</t>
+          <t>Firefly Transform选择器1</t>
         </is>
       </c>
       <c r="G694" t="inlineStr">
         <is>
-          <t>Production independently scheduled Garmentmaker action.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t>生产的独立调度衣匠行动。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>unresolved</t>
         </is>
       </c>
       <c r="J694" t="inlineStr">
@@ -45157,41 +45157,41 @@
     </row>
     <row r="695">
       <c r="B695" t="n">
-        <v>24551</v>
+        <v>24505</v>
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>selector.v1b.aglaea-memosprite.1</t>
+          <t>program.v1b.aglaea.garmentmaker.form</t>
         </is>
       </c>
       <c r="D695" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>CharacterForm</t>
         </is>
       </c>
       <c r="E695" t="inlineStr">
         <is>
-          <t>Aglaea Memosprite Selector 1</t>
+          <t>Garmentmaker Memosprite Form</t>
         </is>
       </c>
       <c r="F695" t="inlineStr">
         <is>
-          <t>Aglaea Memosprite选择器1</t>
+          <t>衣匠忆灵形态</t>
         </is>
       </c>
       <c r="G695" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Production linked-form identity owned by the Aglaea fixture.</t>
         </is>
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>由阿格莱雅探针拥有的生产链接形态标识。</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J695" t="inlineStr">
@@ -45220,41 +45220,41 @@
     </row>
     <row r="696">
       <c r="B696" t="n">
-        <v>24552</v>
+        <v>24506</v>
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>selector.v1b.aglaea-memosprite.2</t>
+          <t>program.v1b.aglaea.memosprite.program</t>
         </is>
       </c>
       <c r="D696" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E696" t="inlineStr">
         <is>
-          <t>Aglaea Memosprite Selector 2</t>
+          <t>Aglaea Memosprite Lifecycle</t>
         </is>
       </c>
       <c r="F696" t="inlineStr">
         <is>
-          <t>Aglaea Memosprite选择器2</t>
+          <t>阿格莱雅忆灵生命周期</t>
         </is>
       </c>
       <c r="G696" t="inlineStr">
         <is>
-          <t>Typed selector promoted with the representative production mechanic.</t>
+          <t>Orders memosprite spawn linked presence and explicit departure.</t>
         </is>
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t>随代表性生产机制一并提升的类型化选择器。</t>
+          <t>按序执行忆灵生成链接在场与显式退场。</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J696" t="inlineStr">
@@ -45283,41 +45283,41 @@
     </row>
     <row r="697">
       <c r="B697" t="n">
-        <v>24601</v>
+        <v>24507</v>
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>program.v1b.firefly.complete-combustion</t>
+          <t>program.v1b.aglaea.garmentmaker-action</t>
         </is>
       </c>
       <c r="D697" t="inlineStr">
         <is>
-          <t>Program</t>
+          <t>Ability</t>
         </is>
       </c>
       <c r="E697" t="inlineStr">
         <is>
-          <t>Complete Combustion Composite Program</t>
+          <t>Garmentmaker Action</t>
         </is>
       </c>
       <c r="F697" t="inlineStr">
         <is>
-          <t>完全燃烧组合程序</t>
+          <t>衣匠行动</t>
         </is>
       </c>
       <c r="G697" t="inlineStr">
         <is>
-          <t>Ordered Complete Combustion state, timeline, form and ability replacement operations.</t>
+          <t>Production independently scheduled Garmentmaker action.</t>
         </is>
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t>按序执行完全燃烧状态、时间线、形态与技能替换操作。</t>
+          <t>生产的独立调度衣匠行动。</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="J697" t="inlineStr">
@@ -45346,36 +45346,36 @@
     </row>
     <row r="698">
       <c r="B698" t="n">
-        <v>24610</v>
+        <v>24551</v>
       </c>
       <c r="C698" t="inlineStr">
         <is>
-          <t>ability.v1b.aglaea.garmentmaker-action</t>
+          <t>selector.v1b.aglaea-memosprite.1</t>
         </is>
       </c>
       <c r="D698" t="inlineStr">
         <is>
-          <t>Ability</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E698" t="inlineStr">
         <is>
-          <t>Garmentmaker Action</t>
+          <t>Aglaea Memosprite Selector 1</t>
         </is>
       </c>
       <c r="F698" t="inlineStr">
         <is>
-          <t>衣匠行动</t>
+          <t>Aglaea Memosprite选择器1</t>
         </is>
       </c>
       <c r="G698" t="inlineStr">
         <is>
-          <t>Catalog-owned independently scheduled Garmentmaker action entry point.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H698" t="inlineStr">
         <is>
-          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I698" t="inlineStr">
@@ -45409,36 +45409,36 @@
     </row>
     <row r="699">
       <c r="B699" t="n">
-        <v>24611</v>
+        <v>24552</v>
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>ability.v1b.firefly.complete-combustion-countdown</t>
+          <t>selector.v1b.aglaea-memosprite.2</t>
         </is>
       </c>
       <c r="D699" t="inlineStr">
         <is>
-          <t>Ability</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E699" t="inlineStr">
         <is>
-          <t>Complete Combustion Countdown</t>
+          <t>Aglaea Memosprite Selector 2</t>
         </is>
       </c>
       <c r="F699" t="inlineStr">
         <is>
-          <t>完全燃烧倒计时</t>
+          <t>Aglaea Memosprite选择器2</t>
         </is>
       </c>
       <c r="G699" t="inlineStr">
         <is>
-          <t>Timeline-only action that ends Firefly's active transformation.</t>
+          <t>Typed selector promoted with the representative production mechanic.</t>
         </is>
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
+          <t>随代表性生产机制一并提升的类型化选择器。</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -45472,41 +45472,41 @@
     </row>
     <row r="700">
       <c r="B700" t="n">
-        <v>24701</v>
+        <v>24601</v>
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.09.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>program.v1b.firefly.complete-combustion</t>
         </is>
       </c>
       <c r="D700" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E700" t="inlineStr">
         <is>
-          <t>DMG Boost: Lightning ThunderAddedRatio</t>
+          <t>Complete Combustion Composite Program</t>
         </is>
       </c>
       <c r="F700" t="inlineStr">
         <is>
-          <t>伤害强化•雷 ThunderAddedRatio</t>
+          <t>完全燃烧组合程序</t>
         </is>
       </c>
       <c r="G700" t="inlineStr">
         <is>
-          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+          <t>Ordered Complete Combustion state, timeline, form and ability replacement operations.</t>
         </is>
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
+          <t>按序执行完全燃烧状态、时间线、形态与技能替换操作。</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="J700" t="inlineStr">
@@ -45535,31 +45535,31 @@
     </row>
     <row r="701">
       <c r="B701" t="n">
-        <v>24702</v>
+        <v>24610</v>
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.10.crit-rate-boost.CriticalChanceBase</t>
+          <t>ability.v1b.aglaea.garmentmaker-action</t>
         </is>
       </c>
       <c r="D701" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>Ability</t>
         </is>
       </c>
       <c r="E701" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost CriticalChanceBase</t>
+          <t>Garmentmaker Action</t>
         </is>
       </c>
       <c r="F701" t="inlineStr">
         <is>
-          <t>暴击率强化 CriticalChanceBase</t>
+          <t>衣匠行动</t>
         </is>
       </c>
       <c r="G701" t="inlineStr">
         <is>
-          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+          <t>Catalog-owned independently scheduled Garmentmaker action entry point.</t>
         </is>
       </c>
       <c r="H701" t="inlineStr">
@@ -45598,31 +45598,31 @@
     </row>
     <row r="702">
       <c r="B702" t="n">
-        <v>24703</v>
+        <v>24611</v>
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.11.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>ability.v1b.firefly.complete-combustion-countdown</t>
         </is>
       </c>
       <c r="D702" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>Ability</t>
         </is>
       </c>
       <c r="E702" t="inlineStr">
         <is>
-          <t>DMG Boost: Lightning ThunderAddedRatio</t>
+          <t>Complete Combustion Countdown</t>
         </is>
       </c>
       <c r="F702" t="inlineStr">
         <is>
-          <t>伤害强化•雷 ThunderAddedRatio</t>
+          <t>完全燃烧倒计时</t>
         </is>
       </c>
       <c r="G702" t="inlineStr">
         <is>
-          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+          <t>Timeline-only action that ends Firefly's active transformation.</t>
         </is>
       </c>
       <c r="H702" t="inlineStr">
@@ -45661,31 +45661,31 @@
     </row>
     <row r="703">
       <c r="B703" t="n">
-        <v>24704</v>
+        <v>24620</v>
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.12.def-boost.DefenceAddedRatio</t>
+          <t>selector.v1b.silver-wolf.owner</t>
         </is>
       </c>
       <c r="D703" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>Selector</t>
         </is>
       </c>
       <c r="E703" t="inlineStr">
         <is>
-          <t>DEF Boost DefenceAddedRatio</t>
+          <t>Silver Wolf Owner Selector</t>
         </is>
       </c>
       <c r="F703" t="inlineStr">
         <is>
-          <t>防御强化 DefenceAddedRatio</t>
+          <t>银狼自身选择器</t>
         </is>
       </c>
       <c r="G703" t="inlineStr">
         <is>
-          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+          <t>Single owner selector for source-bound Silver Wolf resource programs.</t>
         </is>
       </c>
       <c r="H703" t="inlineStr">
@@ -45724,31 +45724,31 @@
     </row>
     <row r="704">
       <c r="B704" t="n">
-        <v>24705</v>
+        <v>24623</v>
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.13.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>program.v1b.silver-wolf.pro-gamer-move</t>
         </is>
       </c>
       <c r="D704" t="inlineStr">
         <is>
-          <t>Modifier</t>
+          <t>Program</t>
         </is>
       </c>
       <c r="E704" t="inlineStr">
         <is>
-          <t>DMG Boost: Lightning ThunderAddedRatio</t>
+          <t>Pro-Gamer Move Program</t>
         </is>
       </c>
       <c r="F704" t="inlineStr">
         <is>
-          <t>伤害强化•雷 ThunderAddedRatio</t>
+          <t>高手玩家程序</t>
         </is>
       </c>
       <c r="G704" t="inlineStr">
         <is>
-          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+          <t>Exact released Elation Skill resource gain program.</t>
         </is>
       </c>
       <c r="H704" t="inlineStr">
@@ -45787,11 +45787,11 @@
     </row>
     <row r="705">
       <c r="B705" t="n">
-        <v>24706</v>
+        <v>24701</v>
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.14.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.aglaea.trace.09.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="D705" t="inlineStr">
@@ -45801,12 +45801,12 @@
       </c>
       <c r="E705" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost CriticalChanceBase</t>
+          <t>DMG Boost: Lightning ThunderAddedRatio</t>
         </is>
       </c>
       <c r="F705" t="inlineStr">
         <is>
-          <t>暴击率强化 CriticalChanceBase</t>
+          <t>伤害强化•雷 ThunderAddedRatio</t>
         </is>
       </c>
       <c r="G705" t="inlineStr">
@@ -45850,11 +45850,11 @@
     </row>
     <row r="706">
       <c r="B706" t="n">
-        <v>24707</v>
+        <v>24702</v>
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.15.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>modifier.character.aglaea.trace.10.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="D706" t="inlineStr">
@@ -45864,12 +45864,12 @@
       </c>
       <c r="E706" t="inlineStr">
         <is>
-          <t>DMG Boost: Lightning ThunderAddedRatio</t>
+          <t>CRIT Rate Boost CriticalChanceBase</t>
         </is>
       </c>
       <c r="F706" t="inlineStr">
         <is>
-          <t>伤害强化•雷 ThunderAddedRatio</t>
+          <t>暴击率强化 CriticalChanceBase</t>
         </is>
       </c>
       <c r="G706" t="inlineStr">
@@ -45913,11 +45913,11 @@
     </row>
     <row r="707">
       <c r="B707" t="n">
-        <v>24708</v>
+        <v>24703</v>
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.16.def-boost.DefenceAddedRatio</t>
+          <t>modifier.character.aglaea.trace.11.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="D707" t="inlineStr">
@@ -45927,12 +45927,12 @@
       </c>
       <c r="E707" t="inlineStr">
         <is>
-          <t>DEF Boost DefenceAddedRatio</t>
+          <t>DMG Boost: Lightning ThunderAddedRatio</t>
         </is>
       </c>
       <c r="F707" t="inlineStr">
         <is>
-          <t>防御强化 DefenceAddedRatio</t>
+          <t>伤害强化•雷 ThunderAddedRatio</t>
         </is>
       </c>
       <c r="G707" t="inlineStr">
@@ -45976,11 +45976,11 @@
     </row>
     <row r="708">
       <c r="B708" t="n">
-        <v>24709</v>
+        <v>24704</v>
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.17.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.aglaea.trace.12.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="D708" t="inlineStr">
@@ -45990,12 +45990,12 @@
       </c>
       <c r="E708" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost CriticalChanceBase</t>
+          <t>DEF Boost DefenceAddedRatio</t>
         </is>
       </c>
       <c r="F708" t="inlineStr">
         <is>
-          <t>暴击率强化 CriticalChanceBase</t>
+          <t>防御强化 DefenceAddedRatio</t>
         </is>
       </c>
       <c r="G708" t="inlineStr">
@@ -46039,11 +46039,11 @@
     </row>
     <row r="709">
       <c r="B709" t="n">
-        <v>24710</v>
+        <v>24705</v>
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>modifier.character.aglaea.trace.18.dmg-boost-lightning.ThunderAddedRatio</t>
+          <t>modifier.character.aglaea.trace.13.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="D709" t="inlineStr">
@@ -46102,11 +46102,11 @@
     </row>
     <row r="710">
       <c r="B710" t="n">
-        <v>24711</v>
+        <v>24706</v>
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.09.dmg-boost-fire.FireAddedRatio</t>
+          <t>modifier.character.aglaea.trace.14.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="D710" t="inlineStr">
@@ -46116,12 +46116,12 @@
       </c>
       <c r="E710" t="inlineStr">
         <is>
-          <t>DMG Boost: Fire FireAddedRatio</t>
+          <t>CRIT Rate Boost CriticalChanceBase</t>
         </is>
       </c>
       <c r="F710" t="inlineStr">
         <is>
-          <t>伤害强化•火 FireAddedRatio</t>
+          <t>暴击率强化 CriticalChanceBase</t>
         </is>
       </c>
       <c r="G710" t="inlineStr">
@@ -46165,11 +46165,11 @@
     </row>
     <row r="711">
       <c r="B711" t="n">
-        <v>24712</v>
+        <v>24707</v>
       </c>
       <c r="C711" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.10.def-boost.DefenceAddedRatio</t>
+          <t>modifier.character.aglaea.trace.15.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="D711" t="inlineStr">
@@ -46179,12 +46179,12 @@
       </c>
       <c r="E711" t="inlineStr">
         <is>
-          <t>DEF Boost DefenceAddedRatio</t>
+          <t>DMG Boost: Lightning ThunderAddedRatio</t>
         </is>
       </c>
       <c r="F711" t="inlineStr">
         <is>
-          <t>防御强化 DefenceAddedRatio</t>
+          <t>伤害强化•雷 ThunderAddedRatio</t>
         </is>
       </c>
       <c r="G711" t="inlineStr">
@@ -46228,11 +46228,11 @@
     </row>
     <row r="712">
       <c r="B712" t="n">
-        <v>24713</v>
+        <v>24708</v>
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.11.dmg-boost-fire.FireAddedRatio</t>
+          <t>modifier.character.aglaea.trace.16.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="D712" t="inlineStr">
@@ -46242,12 +46242,12 @@
       </c>
       <c r="E712" t="inlineStr">
         <is>
-          <t>DMG Boost: Fire FireAddedRatio</t>
+          <t>DEF Boost DefenceAddedRatio</t>
         </is>
       </c>
       <c r="F712" t="inlineStr">
         <is>
-          <t>伤害强化•火 FireAddedRatio</t>
+          <t>防御强化 DefenceAddedRatio</t>
         </is>
       </c>
       <c r="G712" t="inlineStr">
@@ -46291,11 +46291,11 @@
     </row>
     <row r="713">
       <c r="B713" t="n">
-        <v>24714</v>
+        <v>24709</v>
       </c>
       <c r="C713" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.12.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.aglaea.trace.17.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="D713" t="inlineStr">
@@ -46354,11 +46354,11 @@
     </row>
     <row r="714">
       <c r="B714" t="n">
-        <v>24715</v>
+        <v>24710</v>
       </c>
       <c r="C714" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.13.dmg-boost-fire.FireAddedRatio</t>
+          <t>modifier.character.aglaea.trace.18.dmg-boost-lightning.ThunderAddedRatio</t>
         </is>
       </c>
       <c r="D714" t="inlineStr">
@@ -46368,12 +46368,12 @@
       </c>
       <c r="E714" t="inlineStr">
         <is>
-          <t>DMG Boost: Fire FireAddedRatio</t>
+          <t>DMG Boost: Lightning ThunderAddedRatio</t>
         </is>
       </c>
       <c r="F714" t="inlineStr">
         <is>
-          <t>伤害强化•火 FireAddedRatio</t>
+          <t>伤害强化•雷 ThunderAddedRatio</t>
         </is>
       </c>
       <c r="G714" t="inlineStr">
@@ -46417,11 +46417,11 @@
     </row>
     <row r="715">
       <c r="B715" t="n">
-        <v>24716</v>
+        <v>24711</v>
       </c>
       <c r="C715" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.14.def-boost.DefenceAddedRatio</t>
+          <t>modifier.character.asta.trace.09.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="D715" t="inlineStr">
@@ -46431,12 +46431,12 @@
       </c>
       <c r="E715" t="inlineStr">
         <is>
-          <t>DEF Boost DefenceAddedRatio</t>
+          <t>DMG Boost: Fire FireAddedRatio</t>
         </is>
       </c>
       <c r="F715" t="inlineStr">
         <is>
-          <t>防御强化 DefenceAddedRatio</t>
+          <t>伤害强化•火 FireAddedRatio</t>
         </is>
       </c>
       <c r="G715" t="inlineStr">
@@ -46480,11 +46480,11 @@
     </row>
     <row r="716">
       <c r="B716" t="n">
-        <v>24717</v>
+        <v>24712</v>
       </c>
       <c r="C716" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.15.dmg-boost-fire.FireAddedRatio</t>
+          <t>modifier.character.asta.trace.10.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="D716" t="inlineStr">
@@ -46494,12 +46494,12 @@
       </c>
       <c r="E716" t="inlineStr">
         <is>
-          <t>DMG Boost: Fire FireAddedRatio</t>
+          <t>DEF Boost DefenceAddedRatio</t>
         </is>
       </c>
       <c r="F716" t="inlineStr">
         <is>
-          <t>伤害强化•火 FireAddedRatio</t>
+          <t>防御强化 DefenceAddedRatio</t>
         </is>
       </c>
       <c r="G716" t="inlineStr">
@@ -46543,11 +46543,11 @@
     </row>
     <row r="717">
       <c r="B717" t="n">
-        <v>24718</v>
+        <v>24713</v>
       </c>
       <c r="C717" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.16.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.asta.trace.11.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="D717" t="inlineStr">
@@ -46557,12 +46557,12 @@
       </c>
       <c r="E717" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost CriticalChanceBase</t>
+          <t>DMG Boost: Fire FireAddedRatio</t>
         </is>
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>暴击率强化 CriticalChanceBase</t>
+          <t>伤害强化•火 FireAddedRatio</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -46606,11 +46606,11 @@
     </row>
     <row r="718">
       <c r="B718" t="n">
-        <v>24719</v>
+        <v>24714</v>
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.17.def-boost.DefenceAddedRatio</t>
+          <t>modifier.character.asta.trace.12.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="D718" t="inlineStr">
@@ -46620,12 +46620,12 @@
       </c>
       <c r="E718" t="inlineStr">
         <is>
-          <t>DEF Boost DefenceAddedRatio</t>
+          <t>CRIT Rate Boost CriticalChanceBase</t>
         </is>
       </c>
       <c r="F718" t="inlineStr">
         <is>
-          <t>防御强化 DefenceAddedRatio</t>
+          <t>暴击率强化 CriticalChanceBase</t>
         </is>
       </c>
       <c r="G718" t="inlineStr">
@@ -46669,11 +46669,11 @@
     </row>
     <row r="719">
       <c r="B719" t="n">
-        <v>24720</v>
+        <v>24715</v>
       </c>
       <c r="C719" t="inlineStr">
         <is>
-          <t>modifier.character.asta.trace.18.dmg-boost-fire.FireAddedRatio</t>
+          <t>modifier.character.asta.trace.13.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="D719" t="inlineStr">
@@ -46732,11 +46732,11 @@
     </row>
     <row r="720">
       <c r="B720" t="n">
-        <v>24721</v>
+        <v>24716</v>
       </c>
       <c r="C720" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.09.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.asta.trace.14.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="D720" t="inlineStr">
@@ -46746,12 +46746,12 @@
       </c>
       <c r="E720" t="inlineStr">
         <is>
-          <t>ATK Boost AttackAddedRatio</t>
+          <t>DEF Boost DefenceAddedRatio</t>
         </is>
       </c>
       <c r="F720" t="inlineStr">
         <is>
-          <t>攻击强化 AttackAddedRatio</t>
+          <t>防御强化 DefenceAddedRatio</t>
         </is>
       </c>
       <c r="G720" t="inlineStr">
@@ -46795,11 +46795,11 @@
     </row>
     <row r="721">
       <c r="B721" t="n">
-        <v>24722</v>
+        <v>24717</v>
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.10.dmg-boost-physical.PhysicalAddedRatio</t>
+          <t>modifier.character.asta.trace.15.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="D721" t="inlineStr">
@@ -46809,12 +46809,12 @@
       </c>
       <c r="E721" t="inlineStr">
         <is>
-          <t>DMG Boost: Physical PhysicalAddedRatio</t>
+          <t>DMG Boost: Fire FireAddedRatio</t>
         </is>
       </c>
       <c r="F721" t="inlineStr">
         <is>
-          <t>伤害强化•物理 PhysicalAddedRatio</t>
+          <t>伤害强化•火 FireAddedRatio</t>
         </is>
       </c>
       <c r="G721" t="inlineStr">
@@ -46858,11 +46858,11 @@
     </row>
     <row r="722">
       <c r="B722" t="n">
-        <v>24723</v>
+        <v>24718</v>
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.11.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.asta.trace.16.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="D722" t="inlineStr">
@@ -46872,12 +46872,12 @@
       </c>
       <c r="E722" t="inlineStr">
         <is>
-          <t>ATK Boost AttackAddedRatio</t>
+          <t>CRIT Rate Boost CriticalChanceBase</t>
         </is>
       </c>
       <c r="F722" t="inlineStr">
         <is>
-          <t>攻击强化 AttackAddedRatio</t>
+          <t>暴击率强化 CriticalChanceBase</t>
         </is>
       </c>
       <c r="G722" t="inlineStr">
@@ -46921,11 +46921,11 @@
     </row>
     <row r="723">
       <c r="B723" t="n">
-        <v>24724</v>
+        <v>24719</v>
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.12.hp-boost.HPAddedRatio</t>
+          <t>modifier.character.asta.trace.17.def-boost.DefenceAddedRatio</t>
         </is>
       </c>
       <c r="D723" t="inlineStr">
@@ -46935,12 +46935,12 @@
       </c>
       <c r="E723" t="inlineStr">
         <is>
-          <t>HP Boost HPAddedRatio</t>
+          <t>DEF Boost DefenceAddedRatio</t>
         </is>
       </c>
       <c r="F723" t="inlineStr">
         <is>
-          <t>生命强化 HPAddedRatio</t>
+          <t>防御强化 DefenceAddedRatio</t>
         </is>
       </c>
       <c r="G723" t="inlineStr">
@@ -46984,11 +46984,11 @@
     </row>
     <row r="724">
       <c r="B724" t="n">
-        <v>24725</v>
+        <v>24720</v>
       </c>
       <c r="C724" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.13.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.asta.trace.18.dmg-boost-fire.FireAddedRatio</t>
         </is>
       </c>
       <c r="D724" t="inlineStr">
@@ -46998,12 +46998,12 @@
       </c>
       <c r="E724" t="inlineStr">
         <is>
-          <t>ATK Boost AttackAddedRatio</t>
+          <t>DMG Boost: Fire FireAddedRatio</t>
         </is>
       </c>
       <c r="F724" t="inlineStr">
         <is>
-          <t>攻击强化 AttackAddedRatio</t>
+          <t>伤害强化•火 FireAddedRatio</t>
         </is>
       </c>
       <c r="G724" t="inlineStr">
@@ -47047,11 +47047,11 @@
     </row>
     <row r="725">
       <c r="B725" t="n">
-        <v>24726</v>
+        <v>24721</v>
       </c>
       <c r="C725" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.14.dmg-boost-physical.PhysicalAddedRatio</t>
+          <t>modifier.character.clara.trace.09.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D725" t="inlineStr">
@@ -47061,12 +47061,12 @@
       </c>
       <c r="E725" t="inlineStr">
         <is>
-          <t>DMG Boost: Physical PhysicalAddedRatio</t>
+          <t>ATK Boost AttackAddedRatio</t>
         </is>
       </c>
       <c r="F725" t="inlineStr">
         <is>
-          <t>伤害强化•物理 PhysicalAddedRatio</t>
+          <t>攻击强化 AttackAddedRatio</t>
         </is>
       </c>
       <c r="G725" t="inlineStr">
@@ -47110,11 +47110,11 @@
     </row>
     <row r="726">
       <c r="B726" t="n">
-        <v>24727</v>
+        <v>24722</v>
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.15.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.clara.trace.10.dmg-boost-physical.PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="D726" t="inlineStr">
@@ -47124,12 +47124,12 @@
       </c>
       <c r="E726" t="inlineStr">
         <is>
-          <t>ATK Boost AttackAddedRatio</t>
+          <t>DMG Boost: Physical PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="F726" t="inlineStr">
         <is>
-          <t>攻击强化 AttackAddedRatio</t>
+          <t>伤害强化•物理 PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="G726" t="inlineStr">
@@ -47173,11 +47173,11 @@
     </row>
     <row r="727">
       <c r="B727" t="n">
-        <v>24728</v>
+        <v>24723</v>
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.16.hp-boost.HPAddedRatio</t>
+          <t>modifier.character.clara.trace.11.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D727" t="inlineStr">
@@ -47187,12 +47187,12 @@
       </c>
       <c r="E727" t="inlineStr">
         <is>
-          <t>HP Boost HPAddedRatio</t>
+          <t>ATK Boost AttackAddedRatio</t>
         </is>
       </c>
       <c r="F727" t="inlineStr">
         <is>
-          <t>生命强化 HPAddedRatio</t>
+          <t>攻击强化 AttackAddedRatio</t>
         </is>
       </c>
       <c r="G727" t="inlineStr">
@@ -47236,11 +47236,11 @@
     </row>
     <row r="728">
       <c r="B728" t="n">
-        <v>24729</v>
+        <v>24724</v>
       </c>
       <c r="C728" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.17.dmg-boost-physical.PhysicalAddedRatio</t>
+          <t>modifier.character.clara.trace.12.hp-boost.HPAddedRatio</t>
         </is>
       </c>
       <c r="D728" t="inlineStr">
@@ -47250,12 +47250,12 @@
       </c>
       <c r="E728" t="inlineStr">
         <is>
-          <t>DMG Boost: Physical PhysicalAddedRatio</t>
+          <t>HP Boost HPAddedRatio</t>
         </is>
       </c>
       <c r="F728" t="inlineStr">
         <is>
-          <t>伤害强化•物理 PhysicalAddedRatio</t>
+          <t>生命强化 HPAddedRatio</t>
         </is>
       </c>
       <c r="G728" t="inlineStr">
@@ -47299,11 +47299,11 @@
     </row>
     <row r="729">
       <c r="B729" t="n">
-        <v>24730</v>
+        <v>24725</v>
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>modifier.character.clara.trace.18.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.clara.trace.13.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D729" t="inlineStr">
@@ -47362,11 +47362,11 @@
     </row>
     <row r="730">
       <c r="B730" t="n">
-        <v>24731</v>
+        <v>24726</v>
       </c>
       <c r="C730" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.12.break-boost.BreakDamageAddedRatioBase</t>
+          <t>modifier.character.clara.trace.14.dmg-boost-physical.PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="D730" t="inlineStr">
@@ -47376,12 +47376,12 @@
       </c>
       <c r="E730" t="inlineStr">
         <is>
-          <t>Break Boost BreakDamageAddedRatioBase</t>
+          <t>DMG Boost: Physical PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="F730" t="inlineStr">
         <is>
-          <t>击破强化 BreakDamageAddedRatioBase</t>
+          <t>伤害强化•物理 PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="G730" t="inlineStr">
@@ -47425,11 +47425,11 @@
     </row>
     <row r="731">
       <c r="B731" t="n">
-        <v>24732</v>
+        <v>24727</v>
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.13.effect-res-boost.StatusResistanceBase</t>
+          <t>modifier.character.clara.trace.15.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D731" t="inlineStr">
@@ -47439,12 +47439,12 @@
       </c>
       <c r="E731" t="inlineStr">
         <is>
-          <t>Effect RES Boost StatusResistanceBase</t>
+          <t>ATK Boost AttackAddedRatio</t>
         </is>
       </c>
       <c r="F731" t="inlineStr">
         <is>
-          <t>效果抵抗强化 StatusResistanceBase</t>
+          <t>攻击强化 AttackAddedRatio</t>
         </is>
       </c>
       <c r="G731" t="inlineStr">
@@ -47488,11 +47488,11 @@
     </row>
     <row r="732">
       <c r="B732" t="n">
-        <v>24733</v>
+        <v>24728</v>
       </c>
       <c r="C732" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.14.break-boost.BreakDamageAddedRatioBase</t>
+          <t>modifier.character.clara.trace.16.hp-boost.HPAddedRatio</t>
         </is>
       </c>
       <c r="D732" t="inlineStr">
@@ -47502,12 +47502,12 @@
       </c>
       <c r="E732" t="inlineStr">
         <is>
-          <t>Break Boost BreakDamageAddedRatioBase</t>
+          <t>HP Boost HPAddedRatio</t>
         </is>
       </c>
       <c r="F732" t="inlineStr">
         <is>
-          <t>击破强化 BreakDamageAddedRatioBase</t>
+          <t>生命强化 HPAddedRatio</t>
         </is>
       </c>
       <c r="G732" t="inlineStr">
@@ -47551,11 +47551,11 @@
     </row>
     <row r="733">
       <c r="B733" t="n">
-        <v>24734</v>
+        <v>24729</v>
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.15.spd-boost.SpeedDelta</t>
+          <t>modifier.character.clara.trace.17.dmg-boost-physical.PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="D733" t="inlineStr">
@@ -47565,12 +47565,12 @@
       </c>
       <c r="E733" t="inlineStr">
         <is>
-          <t>SPD Boost SpeedDelta</t>
+          <t>DMG Boost: Physical PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="F733" t="inlineStr">
         <is>
-          <t>速度强化 SpeedDelta</t>
+          <t>伤害强化•物理 PhysicalAddedRatio</t>
         </is>
       </c>
       <c r="G733" t="inlineStr">
@@ -47614,11 +47614,11 @@
     </row>
     <row r="734">
       <c r="B734" t="n">
-        <v>24735</v>
+        <v>24730</v>
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.16.break-boost.BreakDamageAddedRatioBase</t>
+          <t>modifier.character.clara.trace.18.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D734" t="inlineStr">
@@ -47628,12 +47628,12 @@
       </c>
       <c r="E734" t="inlineStr">
         <is>
-          <t>Break Boost BreakDamageAddedRatioBase</t>
+          <t>ATK Boost AttackAddedRatio</t>
         </is>
       </c>
       <c r="F734" t="inlineStr">
         <is>
-          <t>击破强化 BreakDamageAddedRatioBase</t>
+          <t>攻击强化 AttackAddedRatio</t>
         </is>
       </c>
       <c r="G734" t="inlineStr">
@@ -47677,11 +47677,11 @@
     </row>
     <row r="735">
       <c r="B735" t="n">
-        <v>24736</v>
+        <v>24731</v>
       </c>
       <c r="C735" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.17.effect-res-boost.StatusResistanceBase</t>
+          <t>modifier.character.firefly.trace.12.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="D735" t="inlineStr">
@@ -47691,12 +47691,12 @@
       </c>
       <c r="E735" t="inlineStr">
         <is>
-          <t>Effect RES Boost StatusResistanceBase</t>
+          <t>Break Boost BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="F735" t="inlineStr">
         <is>
-          <t>效果抵抗强化 StatusResistanceBase</t>
+          <t>击破强化 BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="G735" t="inlineStr">
@@ -47740,11 +47740,11 @@
     </row>
     <row r="736">
       <c r="B736" t="n">
-        <v>24737</v>
+        <v>24732</v>
       </c>
       <c r="C736" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.18.break-boost.BreakDamageAddedRatioBase</t>
+          <t>modifier.character.firefly.trace.13.effect-res-boost.StatusResistanceBase</t>
         </is>
       </c>
       <c r="D736" t="inlineStr">
@@ -47754,12 +47754,12 @@
       </c>
       <c r="E736" t="inlineStr">
         <is>
-          <t>Break Boost BreakDamageAddedRatioBase</t>
+          <t>Effect RES Boost StatusResistanceBase</t>
         </is>
       </c>
       <c r="F736" t="inlineStr">
         <is>
-          <t>击破强化 BreakDamageAddedRatioBase</t>
+          <t>效果抵抗强化 StatusResistanceBase</t>
         </is>
       </c>
       <c r="G736" t="inlineStr">
@@ -47803,11 +47803,11 @@
     </row>
     <row r="737">
       <c r="B737" t="n">
-        <v>24738</v>
+        <v>24733</v>
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.19.spd-boost.SpeedDelta</t>
+          <t>modifier.character.firefly.trace.14.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="D737" t="inlineStr">
@@ -47817,12 +47817,12 @@
       </c>
       <c r="E737" t="inlineStr">
         <is>
-          <t>SPD Boost SpeedDelta</t>
+          <t>Break Boost BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="F737" t="inlineStr">
         <is>
-          <t>速度强化 SpeedDelta</t>
+          <t>击破强化 BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="G737" t="inlineStr">
@@ -47866,11 +47866,11 @@
     </row>
     <row r="738">
       <c r="B738" t="n">
-        <v>24739</v>
+        <v>24734</v>
       </c>
       <c r="C738" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.20.effect-res-boost.StatusResistanceBase</t>
+          <t>modifier.character.firefly.trace.15.spd-boost.SpeedDelta</t>
         </is>
       </c>
       <c r="D738" t="inlineStr">
@@ -47880,12 +47880,12 @@
       </c>
       <c r="E738" t="inlineStr">
         <is>
-          <t>Effect RES Boost StatusResistanceBase</t>
+          <t>SPD Boost SpeedDelta</t>
         </is>
       </c>
       <c r="F738" t="inlineStr">
         <is>
-          <t>效果抵抗强化 StatusResistanceBase</t>
+          <t>速度强化 SpeedDelta</t>
         </is>
       </c>
       <c r="G738" t="inlineStr">
@@ -47929,11 +47929,11 @@
     </row>
     <row r="739">
       <c r="B739" t="n">
-        <v>24740</v>
+        <v>24735</v>
       </c>
       <c r="C739" t="inlineStr">
         <is>
-          <t>modifier.character.firefly.trace.21.break-boost.BreakDamageAddedRatioBase</t>
+          <t>modifier.character.firefly.trace.16.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="D739" t="inlineStr">
@@ -47992,11 +47992,11 @@
     </row>
     <row r="740">
       <c r="B740" t="n">
-        <v>24741</v>
+        <v>24736</v>
       </c>
       <c r="C740" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.11.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.firefly.trace.17.effect-res-boost.StatusResistanceBase</t>
         </is>
       </c>
       <c r="D740" t="inlineStr">
@@ -48006,12 +48006,12 @@
       </c>
       <c r="E740" t="inlineStr">
         <is>
-          <t>ATK Boost AttackAddedRatio</t>
+          <t>Effect RES Boost StatusResistanceBase</t>
         </is>
       </c>
       <c r="F740" t="inlineStr">
         <is>
-          <t>攻击强化 AttackAddedRatio</t>
+          <t>效果抵抗强化 StatusResistanceBase</t>
         </is>
       </c>
       <c r="G740" t="inlineStr">
@@ -48055,11 +48055,11 @@
     </row>
     <row r="741">
       <c r="B741" t="n">
-        <v>24742</v>
+        <v>24737</v>
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.12.effect-hit-rate-boost.StatusProbabilityBase</t>
+          <t>modifier.character.firefly.trace.18.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="D741" t="inlineStr">
@@ -48069,12 +48069,12 @@
       </c>
       <c r="E741" t="inlineStr">
         <is>
-          <t>Effect Hit Rate Boost StatusProbabilityBase</t>
+          <t>Break Boost BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="F741" t="inlineStr">
         <is>
-          <t>效果命中强化 StatusProbabilityBase</t>
+          <t>击破强化 BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="G741" t="inlineStr">
@@ -48118,11 +48118,11 @@
     </row>
     <row r="742">
       <c r="B742" t="n">
-        <v>24743</v>
+        <v>24738</v>
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.13.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.firefly.trace.19.spd-boost.SpeedDelta</t>
         </is>
       </c>
       <c r="D742" t="inlineStr">
@@ -48132,12 +48132,12 @@
       </c>
       <c r="E742" t="inlineStr">
         <is>
-          <t>ATK Boost AttackAddedRatio</t>
+          <t>SPD Boost SpeedDelta</t>
         </is>
       </c>
       <c r="F742" t="inlineStr">
         <is>
-          <t>攻击强化 AttackAddedRatio</t>
+          <t>速度强化 SpeedDelta</t>
         </is>
       </c>
       <c r="G742" t="inlineStr">
@@ -48181,11 +48181,11 @@
     </row>
     <row r="743">
       <c r="B743" t="n">
-        <v>24744</v>
+        <v>24739</v>
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.14.hp-boost.HPAddedRatio</t>
+          <t>modifier.character.firefly.trace.20.effect-res-boost.StatusResistanceBase</t>
         </is>
       </c>
       <c r="D743" t="inlineStr">
@@ -48195,12 +48195,12 @@
       </c>
       <c r="E743" t="inlineStr">
         <is>
-          <t>HP Boost HPAddedRatio</t>
+          <t>Effect RES Boost StatusResistanceBase</t>
         </is>
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>生命强化 HPAddedRatio</t>
+          <t>效果抵抗强化 StatusResistanceBase</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -48244,11 +48244,11 @@
     </row>
     <row r="744">
       <c r="B744" t="n">
-        <v>24745</v>
+        <v>24740</v>
       </c>
       <c r="C744" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.15.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.firefly.trace.21.break-boost.BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="D744" t="inlineStr">
@@ -48258,12 +48258,12 @@
       </c>
       <c r="E744" t="inlineStr">
         <is>
-          <t>ATK Boost AttackAddedRatio</t>
+          <t>Break Boost BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>攻击强化 AttackAddedRatio</t>
+          <t>击破强化 BreakDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
@@ -48307,11 +48307,11 @@
     </row>
     <row r="745">
       <c r="B745" t="n">
-        <v>24746</v>
+        <v>24741</v>
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.16.effect-hit-rate-boost.StatusProbabilityBase</t>
+          <t>modifier.character.kafka.trace.11.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D745" t="inlineStr">
@@ -48321,12 +48321,12 @@
       </c>
       <c r="E745" t="inlineStr">
         <is>
-          <t>Effect Hit Rate Boost StatusProbabilityBase</t>
+          <t>ATK Boost AttackAddedRatio</t>
         </is>
       </c>
       <c r="F745" t="inlineStr">
         <is>
-          <t>效果命中强化 StatusProbabilityBase</t>
+          <t>攻击强化 AttackAddedRatio</t>
         </is>
       </c>
       <c r="G745" t="inlineStr">
@@ -48370,11 +48370,11 @@
     </row>
     <row r="746">
       <c r="B746" t="n">
-        <v>24747</v>
+        <v>24742</v>
       </c>
       <c r="C746" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.17.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.kafka.trace.12.effect-hit-rate-boost.StatusProbabilityBase</t>
         </is>
       </c>
       <c r="D746" t="inlineStr">
@@ -48384,12 +48384,12 @@
       </c>
       <c r="E746" t="inlineStr">
         <is>
-          <t>ATK Boost AttackAddedRatio</t>
+          <t>Effect Hit Rate Boost StatusProbabilityBase</t>
         </is>
       </c>
       <c r="F746" t="inlineStr">
         <is>
-          <t>攻击强化 AttackAddedRatio</t>
+          <t>效果命中强化 StatusProbabilityBase</t>
         </is>
       </c>
       <c r="G746" t="inlineStr">
@@ -48433,11 +48433,11 @@
     </row>
     <row r="747">
       <c r="B747" t="n">
-        <v>24748</v>
+        <v>24743</v>
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.18.hp-boost.HPAddedRatio</t>
+          <t>modifier.character.kafka.trace.13.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D747" t="inlineStr">
@@ -48447,12 +48447,12 @@
       </c>
       <c r="E747" t="inlineStr">
         <is>
-          <t>HP Boost HPAddedRatio</t>
+          <t>ATK Boost AttackAddedRatio</t>
         </is>
       </c>
       <c r="F747" t="inlineStr">
         <is>
-          <t>生命强化 HPAddedRatio</t>
+          <t>攻击强化 AttackAddedRatio</t>
         </is>
       </c>
       <c r="G747" t="inlineStr">
@@ -48496,11 +48496,11 @@
     </row>
     <row r="748">
       <c r="B748" t="n">
-        <v>24749</v>
+        <v>24744</v>
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.19.effect-hit-rate-boost.StatusProbabilityBase</t>
+          <t>modifier.character.kafka.trace.14.hp-boost.HPAddedRatio</t>
         </is>
       </c>
       <c r="D748" t="inlineStr">
@@ -48510,12 +48510,12 @@
       </c>
       <c r="E748" t="inlineStr">
         <is>
-          <t>Effect Hit Rate Boost StatusProbabilityBase</t>
+          <t>HP Boost HPAddedRatio</t>
         </is>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>效果命中强化 StatusProbabilityBase</t>
+          <t>生命强化 HPAddedRatio</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -48559,11 +48559,11 @@
     </row>
     <row r="749">
       <c r="B749" t="n">
-        <v>24750</v>
+        <v>24745</v>
       </c>
       <c r="C749" t="inlineStr">
         <is>
-          <t>modifier.character.kafka.trace.20.atk-boost.AttackAddedRatio</t>
+          <t>modifier.character.kafka.trace.15.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D749" t="inlineStr">
@@ -48622,11 +48622,11 @@
     </row>
     <row r="750">
       <c r="B750" t="n">
-        <v>24751</v>
+        <v>24746</v>
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.09.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.kafka.trace.16.effect-hit-rate-boost.StatusProbabilityBase</t>
         </is>
       </c>
       <c r="D750" t="inlineStr">
@@ -48636,12 +48636,12 @@
       </c>
       <c r="E750" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost CriticalChanceBase</t>
+          <t>Effect Hit Rate Boost StatusProbabilityBase</t>
         </is>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>暴击率强化 CriticalChanceBase</t>
+          <t>效果命中强化 StatusProbabilityBase</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -48685,11 +48685,11 @@
     </row>
     <row r="751">
       <c r="B751" t="n">
-        <v>24752</v>
+        <v>24747</v>
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.10.spd-boost.SpeedDelta</t>
+          <t>modifier.character.kafka.trace.17.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D751" t="inlineStr">
@@ -48699,12 +48699,12 @@
       </c>
       <c r="E751" t="inlineStr">
         <is>
-          <t>SPD Boost SpeedDelta</t>
+          <t>ATK Boost AttackAddedRatio</t>
         </is>
       </c>
       <c r="F751" t="inlineStr">
         <is>
-          <t>速度强化 SpeedDelta</t>
+          <t>攻击强化 AttackAddedRatio</t>
         </is>
       </c>
       <c r="G751" t="inlineStr">
@@ -48748,11 +48748,11 @@
     </row>
     <row r="752">
       <c r="B752" t="n">
-        <v>24753</v>
+        <v>24748</v>
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.11.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.kafka.trace.18.hp-boost.HPAddedRatio</t>
         </is>
       </c>
       <c r="D752" t="inlineStr">
@@ -48762,12 +48762,12 @@
       </c>
       <c r="E752" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost CriticalChanceBase</t>
+          <t>HP Boost HPAddedRatio</t>
         </is>
       </c>
       <c r="F752" t="inlineStr">
         <is>
-          <t>暴击率强化 CriticalChanceBase</t>
+          <t>生命强化 HPAddedRatio</t>
         </is>
       </c>
       <c r="G752" t="inlineStr">
@@ -48811,11 +48811,11 @@
     </row>
     <row r="753">
       <c r="B753" t="n">
-        <v>24754</v>
+        <v>24749</v>
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.12.elation-boost.ElationDamageAddedRatioBase</t>
+          <t>modifier.character.kafka.trace.19.effect-hit-rate-boost.StatusProbabilityBase</t>
         </is>
       </c>
       <c r="D753" t="inlineStr">
@@ -48825,12 +48825,12 @@
       </c>
       <c r="E753" t="inlineStr">
         <is>
-          <t>Elation Boost ElationDamageAddedRatioBase</t>
+          <t>Effect Hit Rate Boost StatusProbabilityBase</t>
         </is>
       </c>
       <c r="F753" t="inlineStr">
         <is>
-          <t>欢愉度强化 ElationDamageAddedRatioBase</t>
+          <t>效果命中强化 StatusProbabilityBase</t>
         </is>
       </c>
       <c r="G753" t="inlineStr">
@@ -48874,11 +48874,11 @@
     </row>
     <row r="754">
       <c r="B754" t="n">
-        <v>24755</v>
+        <v>24750</v>
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.13.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.kafka.trace.20.atk-boost.AttackAddedRatio</t>
         </is>
       </c>
       <c r="D754" t="inlineStr">
@@ -48888,12 +48888,12 @@
       </c>
       <c r="E754" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost CriticalChanceBase</t>
+          <t>ATK Boost AttackAddedRatio</t>
         </is>
       </c>
       <c r="F754" t="inlineStr">
         <is>
-          <t>暴击率强化 CriticalChanceBase</t>
+          <t>攻击强化 AttackAddedRatio</t>
         </is>
       </c>
       <c r="G754" t="inlineStr">
@@ -48937,11 +48937,11 @@
     </row>
     <row r="755">
       <c r="B755" t="n">
-        <v>24756</v>
+        <v>24751</v>
       </c>
       <c r="C755" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.14.spd-boost.SpeedDelta</t>
+          <t>modifier.character.silver-wolf-lv-999.trace.09.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="D755" t="inlineStr">
@@ -48951,12 +48951,12 @@
       </c>
       <c r="E755" t="inlineStr">
         <is>
-          <t>SPD Boost SpeedDelta</t>
+          <t>CRIT Rate Boost CriticalChanceBase</t>
         </is>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>速度强化 SpeedDelta</t>
+          <t>暴击率强化 CriticalChanceBase</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
@@ -49000,11 +49000,11 @@
     </row>
     <row r="756">
       <c r="B756" t="n">
-        <v>24757</v>
+        <v>24752</v>
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.15.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.silver-wolf-lv-999.trace.10.spd-boost.SpeedDelta</t>
         </is>
       </c>
       <c r="D756" t="inlineStr">
@@ -49014,12 +49014,12 @@
       </c>
       <c r="E756" t="inlineStr">
         <is>
-          <t>CRIT Rate Boost CriticalChanceBase</t>
+          <t>SPD Boost SpeedDelta</t>
         </is>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>暴击率强化 CriticalChanceBase</t>
+          <t>速度强化 SpeedDelta</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
@@ -49063,11 +49063,11 @@
     </row>
     <row r="757">
       <c r="B757" t="n">
-        <v>24758</v>
+        <v>24753</v>
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.16.elation-boost.ElationDamageAddedRatioBase</t>
+          <t>modifier.character.silver-wolf-lv-999.trace.11.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="D757" t="inlineStr">
@@ -49077,12 +49077,12 @@
       </c>
       <c r="E757" t="inlineStr">
         <is>
-          <t>Elation Boost ElationDamageAddedRatioBase</t>
+          <t>CRIT Rate Boost CriticalChanceBase</t>
         </is>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>欢愉度强化 ElationDamageAddedRatioBase</t>
+          <t>暴击率强化 CriticalChanceBase</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
@@ -49126,11 +49126,11 @@
     </row>
     <row r="758">
       <c r="B758" t="n">
-        <v>24759</v>
+        <v>24754</v>
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.17.spd-boost.SpeedDelta</t>
+          <t>modifier.character.silver-wolf-lv-999.trace.12.elation-boost.ElationDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="D758" t="inlineStr">
@@ -49140,12 +49140,12 @@
       </c>
       <c r="E758" t="inlineStr">
         <is>
-          <t>SPD Boost SpeedDelta</t>
+          <t>Elation Boost ElationDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="F758" t="inlineStr">
         <is>
-          <t>速度强化 SpeedDelta</t>
+          <t>欢愉度强化 ElationDamageAddedRatioBase</t>
         </is>
       </c>
       <c r="G758" t="inlineStr">
@@ -49189,11 +49189,11 @@
     </row>
     <row r="759">
       <c r="B759" t="n">
-        <v>24760</v>
+        <v>24755</v>
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>modifier.character.silver-wolf-lv-999.trace.18.crit-rate-boost.CriticalChanceBase</t>
+          <t>modifier.character.silver-wolf-lv-999.trace.13.crit-rate-boost.CriticalChanceBase</t>
         </is>
       </c>
       <c r="D759" t="inlineStr">
@@ -49252,31 +49252,31 @@
     </row>
     <row r="760">
       <c r="B760" t="n">
-        <v>24990</v>
+        <v>24756</v>
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>selector.v1b.trace-minor.owner</t>
+          <t>modifier.character.silver-wolf-lv-999.trace.14.spd-boost.SpeedDelta</t>
         </is>
       </c>
       <c r="D760" t="inlineStr">
         <is>
-          <t>Selector</t>
+          <t>Modifier</t>
         </is>
       </c>
       <c r="E760" t="inlineStr">
         <is>
-          <t>V1B Minor Trace Owner Selector</t>
+          <t>SPD Boost SpeedDelta</t>
         </is>
       </c>
       <c r="F760" t="inlineStr">
         <is>
-          <t>V1B小行迹Owner选择器</t>
+          <t>速度强化 SpeedDelta</t>
         </is>
       </c>
       <c r="G760" t="inlineStr">
         <is>
-          <t>Generic single-subject selector used by production minor-Trace modifiers.</t>
+          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
         </is>
       </c>
       <c r="H760" t="inlineStr">
@@ -49315,62 +49315,377 @@
     </row>
     <row r="761">
       <c r="B761" t="n">
+        <v>24757</v>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>modifier.character.silver-wolf-lv-999.trace.15.crit-rate-boost.CriticalChanceBase</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>CRIT Rate Boost CriticalChanceBase</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>暴击率强化 CriticalChanceBase</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="J761" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="L761" t="b">
+        <v>1</v>
+      </c>
+      <c r="M761" t="inlineStr">
+        <is>
+          <t>DataReady</t>
+        </is>
+      </c>
+      <c r="N761" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="B762" t="n">
+        <v>24758</v>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>modifier.character.silver-wolf-lv-999.trace.16.elation-boost.ElationDamageAddedRatioBase</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Elation Boost ElationDamageAddedRatioBase</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>欢愉度强化 ElationDamageAddedRatioBase</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="J762" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="K762" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="L762" t="b">
+        <v>1</v>
+      </c>
+      <c r="M762" t="inlineStr">
+        <is>
+          <t>DataReady</t>
+        </is>
+      </c>
+      <c r="N762" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="B763" t="n">
+        <v>24759</v>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>modifier.character.silver-wolf-lv-999.trace.17.spd-boost.SpeedDelta</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>SPD Boost SpeedDelta</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>速度强化 SpeedDelta</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="J763" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="L763" t="b">
+        <v>1</v>
+      </c>
+      <c r="M763" t="inlineStr">
+        <is>
+          <t>DataReady</t>
+        </is>
+      </c>
+      <c r="N763" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="B764" t="n">
+        <v>24760</v>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>modifier.character.silver-wolf-lv-999.trace.18.crit-rate-boost.CriticalChanceBase</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Modifier</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>CRIT Rate Boost CriticalChanceBase</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>暴击率强化 CriticalChanceBase</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>Exact prepared minor-Trace stat addition compiled as a persistent modifier.</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="J764" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="L764" t="b">
+        <v>1</v>
+      </c>
+      <c r="M764" t="inlineStr">
+        <is>
+          <t>DataReady</t>
+        </is>
+      </c>
+      <c r="N764" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="B765" t="n">
+        <v>24990</v>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>selector.v1b.trace-minor.owner</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Selector</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>V1B Minor Trace Owner Selector</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>V1B小行迹Owner选择器</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>Generic single-subject selector used by production minor-Trace modifiers.</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="J765" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="L765" t="b">
+        <v>1</v>
+      </c>
+      <c r="M765" t="inlineStr">
+        <is>
+          <t>DataReady</t>
+        </is>
+      </c>
+      <c r="N765" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="B766" t="n">
         <v>24991</v>
       </c>
-      <c r="C761" t="inlineStr">
+      <c r="C766" t="inlineStr">
         <is>
           <t>selector.v1b.trace-minor.currentsubject</t>
         </is>
       </c>
-      <c r="D761" t="inlineStr">
+      <c r="D766" t="inlineStr">
         <is>
           <t>Selector</t>
         </is>
       </c>
-      <c r="E761" t="inlineStr">
+      <c r="E766" t="inlineStr">
         <is>
           <t>V1B Minor Trace Current Subject Selector</t>
         </is>
       </c>
-      <c r="F761" t="inlineStr">
+      <c r="F766" t="inlineStr">
         <is>
           <t>V1B小行迹Current Subject选择器</t>
         </is>
       </c>
-      <c r="G761" t="inlineStr">
+      <c r="G766" t="inlineStr">
         <is>
           <t>Generic single-subject selector used by production minor-Trace modifiers.</t>
         </is>
       </c>
-      <c r="H761" t="inlineStr">
+      <c r="H766" t="inlineStr">
         <is>
           <t>版本4.4准备数据中完整转录并绑定来源的战斗内容。</t>
         </is>
       </c>
-      <c r="I761" t="inlineStr">
-        <is>
-          <t>unresolved</t>
-        </is>
-      </c>
-      <c r="J761" t="inlineStr">
-        <is>
-          <t>4.4</t>
-        </is>
-      </c>
-      <c r="K761" t="inlineStr">
-        <is>
-          <t>Released</t>
-        </is>
-      </c>
-      <c r="L761" t="b">
-        <v>1</v>
-      </c>
-      <c r="M761" t="inlineStr">
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>unresolved</t>
+        </is>
+      </c>
+      <c r="J766" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="K766" t="inlineStr">
+        <is>
+          <t>Released</t>
+        </is>
+      </c>
+      <c r="L766" t="b">
+        <v>1</v>
+      </c>
+      <c r="M766" t="inlineStr">
         <is>
           <t>DataReady</t>
         </is>
       </c>
-      <c r="N761" t="inlineStr">
+      <c r="N766" t="inlineStr">
         <is>
           <t>1</t>
         </is>
